--- a/planilha_robo_iss.xlsx
+++ b/planilha_robo_iss.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geise Ferreira\OneDrive\Documentos\Robô Iss Fortaleza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Documents\WorkSpace\RoboIss\RoboIssFortaleza\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9A5658-FE77-4B01-B337-57338E7994A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D20DDDE-D2B6-4584-8710-F41EECDE253C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9FBABEF1-810A-4A33-A2A2-C20BD378460C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9FBABEF1-810A-4A33-A2A2-C20BD378460C}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Estados" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$H$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5653" uniqueCount="5348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5704" uniqueCount="5367">
   <si>
     <t>CNPJ</t>
   </si>
@@ -15991,107 +15991,167 @@
     <t>E</t>
   </si>
   <si>
-    <t>43.596.411/0001-02</t>
-  </si>
-  <si>
-    <t>4301</t>
-  </si>
-  <si>
-    <t>13.021.784/0001-86</t>
-  </si>
-  <si>
-    <t>2643524</t>
-  </si>
-  <si>
-    <t>4317</t>
-  </si>
-  <si>
-    <t>06.913.315/0001-06</t>
-  </si>
-  <si>
-    <t>4935</t>
-  </si>
-  <si>
-    <t>13.581.630/0001-49</t>
-  </si>
-  <si>
-    <t>128868</t>
-  </si>
-  <si>
-    <t>20.377.877/0001-03</t>
-  </si>
-  <si>
-    <t>668</t>
-  </si>
-  <si>
-    <t>11.973.134/0001-05</t>
-  </si>
-  <si>
-    <t>4296238</t>
-  </si>
-  <si>
-    <t>02.972.166/0001-03</t>
-  </si>
-  <si>
-    <t>9030</t>
-  </si>
-  <si>
-    <t>9023</t>
-  </si>
-  <si>
-    <t>10.423.136/0001-11</t>
-  </si>
-  <si>
-    <t>178841</t>
-  </si>
-  <si>
-    <t>31.363.193/0001-79</t>
-  </si>
-  <si>
-    <t>740</t>
-  </si>
-  <si>
-    <t>25.322.949/0002-10</t>
-  </si>
-  <si>
-    <t>20036</t>
-  </si>
-  <si>
-    <t>36.952.966/0001-76</t>
-  </si>
-  <si>
-    <t>3626</t>
-  </si>
-  <si>
-    <t>39.886.875/0001-78</t>
-  </si>
-  <si>
-    <t>15895</t>
-  </si>
-  <si>
-    <t>13.347.016/0001-17</t>
-  </si>
-  <si>
-    <t>109088942</t>
-  </si>
-  <si>
-    <t>47.076.679/0001-66</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>25.012.398/0001-07</t>
-  </si>
-  <si>
-    <t>12926212</t>
+    <t>SAO PAULO</t>
+  </si>
+  <si>
+    <t>RIO DE JANEIRO</t>
+  </si>
+  <si>
+    <t>62.896.223/0001-36</t>
+  </si>
+  <si>
+    <t>62.162.601/0001-58</t>
+  </si>
+  <si>
+    <t>62.024.082/0001-61</t>
+  </si>
+  <si>
+    <t>59.782.473/0001-30</t>
+  </si>
+  <si>
+    <t>35.502.313/0001-22</t>
+  </si>
+  <si>
+    <t>58.362.073/0001-03</t>
+  </si>
+  <si>
+    <t>57.441.767/0001-73</t>
+  </si>
+  <si>
+    <t>54.542.308/0001-98</t>
+  </si>
+  <si>
+    <t>53.522.738/0001-85</t>
+  </si>
+  <si>
+    <t>45.880.894/0001-90</t>
+  </si>
+  <si>
+    <t>51.822.788/0001-52</t>
+  </si>
+  <si>
+    <t>33.672.904/0001-12</t>
+  </si>
+  <si>
+    <t>61.741.772/0001-79</t>
+  </si>
+  <si>
+    <t>41.638.913/0001-15</t>
+  </si>
+  <si>
+    <t>46.778.961/0001-22</t>
+  </si>
+  <si>
+    <t>46.086.313/0001-05</t>
+  </si>
+  <si>
+    <t>43.539.191/0001-77</t>
+  </si>
+  <si>
+    <t>40.305.652/0001-59</t>
+  </si>
+  <si>
+    <t>40.357.918/0001-07</t>
+  </si>
+  <si>
+    <t>40.677.444/0001-80</t>
+  </si>
+  <si>
+    <t>30.186.096/0001-95</t>
+  </si>
+  <si>
+    <t>36.528.930/0001-60</t>
+  </si>
+  <si>
+    <t>29.559.232/0001-66</t>
+  </si>
+  <si>
+    <t>45.268.215/0001-26</t>
+  </si>
+  <si>
+    <t>42.494.318/0001-16</t>
+  </si>
+  <si>
+    <t>18.225.822/0001-36</t>
+  </si>
+  <si>
+    <t>45.585.795/0001-85</t>
+  </si>
+  <si>
+    <t>22.076.773/0001-94</t>
+  </si>
+  <si>
+    <t>16.804.240/0001-89</t>
+  </si>
+  <si>
+    <t>OCARA</t>
+  </si>
+  <si>
+    <t>SOBRAL</t>
+  </si>
+  <si>
+    <t>SÃO PAULO</t>
+  </si>
+  <si>
+    <t>SOLONOPOLE</t>
+  </si>
+  <si>
+    <t>TERESINA</t>
+  </si>
+  <si>
+    <t>NOVA OLINDA</t>
+  </si>
+  <si>
+    <t>ALCANTARAS</t>
+  </si>
+  <si>
+    <t>COREAU</t>
+  </si>
+  <si>
+    <t>RECIFE</t>
+  </si>
+  <si>
+    <t>QUIXADA</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>HORIZONTE</t>
+  </si>
+  <si>
+    <t>JAGUARIBE</t>
+  </si>
+  <si>
+    <t>FORTALEZA</t>
+  </si>
+  <si>
+    <t>SAO SIMAO</t>
+  </si>
+  <si>
+    <t>JUIZ DE FORA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>VOTORANTIM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="###,###,###,##0.00"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -16106,9 +16166,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -16137,22 +16214,43 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{FEF274E4-6514-42DA-A7F2-FEE3ED085583}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -16485,24 +16583,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{396D9450-A7E8-45E5-B6FB-0B27BBB86E62}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:H27"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I45"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8" style="4"/>
+    <col min="13" max="13" width="8" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -16528,483 +16628,975 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>5318</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="7">
+        <v>3</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46107</v>
+      </c>
+      <c r="D2" s="7">
+        <v>8550302</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>5347</v>
+      </c>
+      <c r="H2" s="11">
+        <v>3750</v>
+      </c>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
         <v>5319</v>
       </c>
-      <c r="C2" s="4">
-        <v>45804</v>
-      </c>
-      <c r="D2">
-        <v>6203100</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B3" s="7">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8">
+        <v>46100</v>
+      </c>
+      <c r="D3" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>4329</v>
-      </c>
-      <c r="H2" s="6">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>5348</v>
+      </c>
+      <c r="H3" s="11">
+        <v>13300</v>
+      </c>
+      <c r="I3" s="12"/>
+    </row>
+    <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>5320</v>
+      </c>
+      <c r="B4" s="7">
+        <v>6</v>
+      </c>
+      <c r="C4" s="8">
+        <v>46087</v>
+      </c>
+      <c r="D4" s="7">
+        <v>8230001</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>5349</v>
+      </c>
+      <c r="H4" s="11">
+        <v>21360</v>
+      </c>
+      <c r="I4" s="12"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>5321</v>
+      </c>
+      <c r="B5" s="7">
+        <v>9</v>
+      </c>
+      <c r="C5" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D5" s="7">
+        <v>821130002</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>5350</v>
+      </c>
+      <c r="H5" s="11">
+        <v>17160</v>
+      </c>
+      <c r="I5" s="12"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>5322</v>
+      </c>
+      <c r="B6" s="7">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8">
+        <v>45989</v>
+      </c>
+      <c r="D6" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>5351</v>
+      </c>
+      <c r="H6" s="11">
+        <v>3200</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>5322</v>
+      </c>
+      <c r="B7" s="7">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8">
+        <v>45989</v>
+      </c>
+      <c r="D7" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>5351</v>
+      </c>
+      <c r="H7" s="11">
+        <v>4000</v>
+      </c>
+      <c r="I7" s="12"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>5323</v>
+      </c>
+      <c r="B8" s="7">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D8" s="7">
+        <v>859969901</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>5352</v>
+      </c>
+      <c r="H8" s="11">
+        <v>17160</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>5324</v>
+      </c>
+      <c r="B9" s="7">
+        <v>20</v>
+      </c>
+      <c r="C9" s="8">
+        <v>45986</v>
+      </c>
+      <c r="D9" s="7">
+        <v>855030202</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>5348</v>
+      </c>
+      <c r="H9" s="11">
+        <v>13300</v>
+      </c>
+      <c r="I9" s="12"/>
+    </row>
+    <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>5325</v>
+      </c>
+      <c r="B10" s="7">
+        <v>23</v>
+      </c>
+      <c r="C10" s="8">
+        <v>45980</v>
+      </c>
+      <c r="D10" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>5353</v>
+      </c>
+      <c r="H10" s="11">
+        <v>13832</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>5326</v>
+      </c>
+      <c r="B11" s="7">
+        <v>23</v>
+      </c>
+      <c r="C11" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D11" s="7">
+        <v>722070001</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>5354</v>
+      </c>
+      <c r="H11" s="11">
+        <v>13300</v>
+      </c>
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>5327</v>
+      </c>
+      <c r="B12" s="7">
+        <v>24</v>
+      </c>
+      <c r="C12" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D12" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>5355</v>
+      </c>
+      <c r="H12" s="11">
+        <v>8300</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>5328</v>
+      </c>
+      <c r="B13" s="7">
+        <v>29</v>
+      </c>
+      <c r="C13" s="8">
+        <v>45976</v>
+      </c>
+      <c r="D13" s="7">
+        <v>8550302</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>5356</v>
+      </c>
+      <c r="H13" s="11">
+        <v>2080</v>
+      </c>
+      <c r="I13" s="12"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>5329</v>
+      </c>
+      <c r="B14" s="7">
+        <v>35</v>
+      </c>
+      <c r="C14" s="8">
+        <v>45986</v>
+      </c>
+      <c r="D14" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>5351</v>
+      </c>
+      <c r="H14" s="11">
+        <v>3200</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>5329</v>
+      </c>
+      <c r="B15" s="7">
+        <v>36</v>
+      </c>
+      <c r="C15" s="8">
+        <v>45986</v>
+      </c>
+      <c r="D15" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>5351</v>
+      </c>
+      <c r="H15" s="11">
+        <v>4000</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>5330</v>
+      </c>
+      <c r="B16" s="7">
+        <v>37</v>
+      </c>
+      <c r="C16" s="8">
+        <v>45966</v>
+      </c>
+      <c r="D16" s="7">
+        <v>8230001</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>5357</v>
+      </c>
+      <c r="H16" s="11">
+        <v>5355</v>
+      </c>
+      <c r="I16" s="12"/>
+    </row>
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>5331</v>
+      </c>
+      <c r="B17" s="7">
+        <v>39</v>
+      </c>
+      <c r="C17" s="8">
+        <v>45989</v>
+      </c>
+      <c r="D17" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>5316</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5320</v>
-      </c>
-      <c r="C3" s="4">
-        <v>45800</v>
-      </c>
-      <c r="D3">
-        <v>6920602</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="H17" s="11">
+        <v>8950</v>
+      </c>
+      <c r="I17" s="12"/>
+    </row>
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>5332</v>
+      </c>
+      <c r="B18" s="7">
+        <v>44</v>
+      </c>
+      <c r="C18" s="8">
+        <v>45986</v>
+      </c>
+      <c r="D18" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>4575</v>
-      </c>
-      <c r="H3" s="6">
-        <v>6585.18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5316</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="G18" s="10" t="s">
+        <v>5358</v>
+      </c>
+      <c r="H18" s="11">
+        <v>19645</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>5333</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46</v>
+      </c>
+      <c r="C19" s="8">
+        <v>45980</v>
+      </c>
+      <c r="D19" s="7">
+        <v>859969901</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>5359</v>
+      </c>
+      <c r="H19" s="11">
+        <v>14664</v>
+      </c>
+      <c r="I19" s="12"/>
+    </row>
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>5334</v>
+      </c>
+      <c r="B20" s="7">
+        <v>55</v>
+      </c>
+      <c r="C20" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D20" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>5348</v>
+      </c>
+      <c r="H20" s="11">
+        <v>15765</v>
+      </c>
+      <c r="I20" s="12"/>
+    </row>
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>5335</v>
+      </c>
+      <c r="B21" s="7">
+        <v>60</v>
+      </c>
+      <c r="C21" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D21" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>5360</v>
+      </c>
+      <c r="H21" s="11">
+        <v>18190</v>
+      </c>
+      <c r="I21" s="12"/>
+    </row>
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>5336</v>
+      </c>
+      <c r="B22" s="7">
+        <v>63</v>
+      </c>
+      <c r="C22" s="8">
+        <v>45980</v>
+      </c>
+      <c r="D22" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>5348</v>
+      </c>
+      <c r="H22" s="11">
+        <v>19645</v>
+      </c>
+      <c r="I22" s="12"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>5337</v>
+      </c>
+      <c r="B23" s="7">
+        <v>63</v>
+      </c>
+      <c r="C23" s="8">
+        <v>45988</v>
+      </c>
+      <c r="D23" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>5361</v>
+      </c>
+      <c r="H23" s="11">
+        <v>19645</v>
+      </c>
+      <c r="I23" s="12"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="6" t="s">
+        <v>5338</v>
+      </c>
+      <c r="B24" s="7">
+        <v>65</v>
+      </c>
+      <c r="C24" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D24" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>5362</v>
+      </c>
+      <c r="H24" s="11">
+        <v>8600</v>
+      </c>
+      <c r="I24" s="12"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>5339</v>
+      </c>
+      <c r="B25" s="7">
+        <v>78</v>
+      </c>
+      <c r="C25" s="8">
+        <v>45985</v>
+      </c>
+      <c r="D25" s="7">
+        <v>859960401</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>5363</v>
+      </c>
+      <c r="H25" s="11">
+        <v>18190</v>
+      </c>
+      <c r="I25" s="12"/>
+    </row>
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="6" t="s">
+        <v>5340</v>
+      </c>
+      <c r="B26" s="7">
+        <v>98</v>
+      </c>
+      <c r="C26" s="8">
+        <v>45964</v>
+      </c>
+      <c r="D26" s="7">
+        <v>5811500</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>5317</v>
       </c>
-      <c r="C4" s="4">
-        <v>45797</v>
-      </c>
-      <c r="D4">
-        <v>6920602</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H26" s="11">
+        <v>6000</v>
+      </c>
+      <c r="I26" s="12"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>5341</v>
+      </c>
+      <c r="B27" s="7">
+        <v>99</v>
+      </c>
+      <c r="C27" s="8">
+        <v>45981</v>
+      </c>
+      <c r="D27" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F27" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>5364</v>
+      </c>
+      <c r="H27" s="11">
+        <v>14700</v>
+      </c>
+      <c r="I27" s="12"/>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>5342</v>
+      </c>
+      <c r="B28" s="7">
+        <v>116</v>
+      </c>
+      <c r="C28" s="8">
+        <v>45975</v>
+      </c>
+      <c r="D28" s="7">
+        <v>7220700</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>5317</v>
+      </c>
+      <c r="H28" s="11">
+        <v>43922</v>
+      </c>
+      <c r="I28" s="12"/>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>5343</v>
+      </c>
+      <c r="B29" s="7">
+        <v>157</v>
+      </c>
+      <c r="C29" s="8">
+        <v>45988</v>
+      </c>
+      <c r="D29" s="7">
+        <v>8599699</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>4575</v>
-      </c>
-      <c r="H4" s="6">
-        <v>8397.86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5321</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5322</v>
-      </c>
-      <c r="C5" s="4">
-        <v>45793</v>
-      </c>
-      <c r="D5">
-        <v>8230001</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="G29" s="10" t="s">
+        <v>5349</v>
+      </c>
+      <c r="H29" s="11">
+        <v>30666</v>
+      </c>
+      <c r="I29" s="12"/>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
+        <v>5344</v>
+      </c>
+      <c r="B30" s="7">
+        <v>162</v>
+      </c>
+      <c r="C30" s="8">
+        <v>45972</v>
+      </c>
+      <c r="D30" s="7">
+        <v>8599604</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F30" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="G30" s="10" t="s">
+        <v>5365</v>
+      </c>
+      <c r="H30" s="11">
+        <v>7000</v>
+      </c>
+      <c r="I30" s="12"/>
+    </row>
+    <row r="31" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="6" t="s">
+        <v>5345</v>
+      </c>
+      <c r="B31" s="7">
+        <v>171</v>
+      </c>
+      <c r="C31" s="8">
+        <v>45965</v>
+      </c>
+      <c r="D31" s="7">
+        <v>855030202</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>5363</v>
+      </c>
+      <c r="H31" s="11">
+        <v>11000</v>
+      </c>
+      <c r="I31" s="12"/>
+    </row>
+    <row r="32" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="6" t="s">
+        <v>5345</v>
+      </c>
+      <c r="B32" s="7">
+        <v>172</v>
+      </c>
+      <c r="C32" s="8">
+        <v>45965</v>
+      </c>
+      <c r="D32" s="7">
+        <v>855030202</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>5363</v>
+      </c>
+      <c r="H32" s="11">
         <v>15000</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>5323</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>5324</v>
-      </c>
-      <c r="C6" s="4">
-        <v>45790</v>
-      </c>
-      <c r="D6">
-        <v>6203100</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="I32" s="12"/>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6" t="s">
+        <v>5346</v>
+      </c>
+      <c r="B33" s="7">
+        <v>415</v>
+      </c>
+      <c r="C33" s="8">
+        <v>45964</v>
+      </c>
+      <c r="D33" s="7">
+        <v>620310001</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>3070</v>
-      </c>
-      <c r="H6" s="6">
-        <v>403.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5325</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>5326</v>
-      </c>
-      <c r="C7" s="4">
-        <v>45789</v>
-      </c>
-      <c r="D7">
-        <v>6209100</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F33" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H33" s="11">
+        <v>7826.71</v>
+      </c>
+      <c r="I33" s="12"/>
+    </row>
+    <row r="34" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>5346</v>
+      </c>
+      <c r="B34" s="7">
+        <v>416</v>
+      </c>
+      <c r="C34" s="8">
+        <v>45964</v>
+      </c>
+      <c r="D34" s="7">
+        <v>620310001</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>3472</v>
-      </c>
-      <c r="H7" s="6">
-        <v>9107.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5327</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>5328</v>
-      </c>
-      <c r="C8" s="4">
-        <v>45787</v>
-      </c>
-      <c r="D8">
-        <v>6550200</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F34" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H34" s="11">
+        <v>11730.85</v>
+      </c>
+      <c r="I34" s="12"/>
+    </row>
+    <row r="35" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>5346</v>
+      </c>
+      <c r="B35" s="7">
+        <v>417</v>
+      </c>
+      <c r="C35" s="8">
+        <v>45964</v>
+      </c>
+      <c r="D35" s="7">
+        <v>620310001</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>5315</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="6">
-        <v>170.8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5329</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>5330</v>
-      </c>
-      <c r="C9" s="4">
-        <v>45784</v>
-      </c>
-      <c r="D9">
-        <v>8630503</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>5329</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>5331</v>
-      </c>
-      <c r="C10" s="4">
-        <v>45784</v>
-      </c>
-      <c r="D10">
-        <v>8630503</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="H10" s="6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5332</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>5333</v>
-      </c>
-      <c r="C11" s="4">
-        <v>45779</v>
-      </c>
-      <c r="D11">
-        <v>6319400</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>967</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1681.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>5334</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5335</v>
-      </c>
-      <c r="C12" s="4">
-        <v>45782</v>
-      </c>
-      <c r="D12">
-        <v>6319400</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="6">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>5336</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5337</v>
-      </c>
-      <c r="C13" s="4">
-        <v>45779</v>
-      </c>
-      <c r="D13">
-        <v>6203100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>4473</v>
-      </c>
-      <c r="H13" s="6">
-        <v>6194.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>5338</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>5339</v>
-      </c>
-      <c r="C14" s="4">
-        <v>45780</v>
-      </c>
-      <c r="D14">
-        <v>8599604</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>3645</v>
-      </c>
-      <c r="H14" s="6">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>5340</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5341</v>
-      </c>
-      <c r="C15" s="4">
-        <v>45780</v>
-      </c>
-      <c r="D15">
-        <v>9521500</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H15" s="6">
-        <v>137.78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>5342</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>5343</v>
-      </c>
-      <c r="C16" s="4">
-        <v>45779</v>
-      </c>
-      <c r="D16">
-        <v>8220200</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F16" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="6">
-        <v>169.79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>5344</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>5345</v>
-      </c>
-      <c r="C17" s="4">
-        <v>45779</v>
-      </c>
-      <c r="D17">
-        <v>6911701</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F17" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>5346</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>5347</v>
-      </c>
-      <c r="C18" s="4">
-        <v>45778</v>
-      </c>
-      <c r="D18">
-        <v>6319400</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5315</v>
-      </c>
-      <c r="F18" t="s">
-        <v>7</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H18" s="6">
-        <v>5600</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="4"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="4"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G35" s="10" t="s">
+        <v>5366</v>
+      </c>
+      <c r="H35" s="11">
+        <v>2290.34</v>
+      </c>
+      <c r="I35" s="12"/>
+    </row>
+    <row r="36" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="4"/>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="4"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B45" s="4"/>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H17">
+    <sortCondition ref="A2:A17"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CD000109-B85C-47F8-A2C5-5B9B46A7FD78}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{006018E0-E219-4EDD-9FD9-87C152F398E7}">
+          <x14:formula1>
+            <xm:f>OFFSET(Estados!$A$2,0,MATCH(#REF!,Estados!$A$1:$AA$1,0)-1,COUNTA(OFFSET(Estados!$A$2:$A$1048576,0,MATCH(#REF!,Estados!$A$1:$AA$1,0)-1)),1)</xm:f>
+          </x14:formula1>
+          <xm:sqref>F7 F11 F16 F2:F4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DD5DA4DB-62E5-4198-861D-CB966F2BAC28}">
           <x14:formula1>
             <xm:f>OFFSET(Estados!$A$2,0,MATCH(F2,Estados!$A$1:$AA$1,0)-1,COUNTA(OFFSET(Estados!$A$2:$A$1048576,0,MATCH(F2,Estados!$A$1:$AA$1,0)-1)),1)</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G20</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E024BE1E-150B-45A1-9671-840F7A9D0189}">
-          <x14:formula1>
-            <xm:f>Estados!$A$1:$AA$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>F3:F4</xm:sqref>
+          <xm:sqref>G2:G17 G21:G35</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -17015,9 +17607,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3247C94-18FE-46DE-9058-9EC7D8BAE706}">
   <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5301</v>
       </c>
@@ -17025,7 +17617,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5302</v>
       </c>
@@ -17033,7 +17625,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5303</v>
       </c>
@@ -17041,7 +17633,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5304</v>
       </c>
@@ -17049,7 +17641,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5305</v>
       </c>
@@ -17057,7 +17649,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5306</v>
       </c>
@@ -17065,7 +17657,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5307</v>
       </c>
@@ -17073,7 +17665,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5308</v>
       </c>
@@ -17081,7 +17673,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5309</v>
       </c>
@@ -17089,7 +17681,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5310</v>
       </c>
@@ -17097,7 +17689,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5311</v>
       </c>
@@ -17105,7 +17697,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5312</v>
       </c>
@@ -17119,37 +17711,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603F22A5-AC69-4E4B-87C8-C926E4C4D730}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA855"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="24" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="25.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="29.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="25.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="27" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="24.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="29.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="26.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="26.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="27.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -17232,7 +17824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>41</v>
       </c>
@@ -17315,7 +17907,7 @@
         <v>5179</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>241</v>
       </c>
@@ -17398,7 +17990,7 @@
         <v>5180</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>242</v>
       </c>
@@ -17481,7 +18073,7 @@
         <v>5181</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>42</v>
       </c>
@@ -17564,7 +18156,7 @@
         <v>5182</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>43</v>
       </c>
@@ -17647,7 +18239,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -17730,7 +18322,7 @@
         <v>5183</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>243</v>
       </c>
@@ -17813,7 +18405,7 @@
         <v>5184</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
@@ -17896,7 +18488,7 @@
         <v>5185</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
@@ -17979,7 +18571,7 @@
         <v>5186</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
@@ -18062,7 +18654,7 @@
         <v>5187</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>244</v>
       </c>
@@ -18145,7 +18737,7 @@
         <v>5188</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>48</v>
       </c>
@@ -18228,7 +18820,7 @@
         <v>5189</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>49</v>
       </c>
@@ -18311,7 +18903,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>245</v>
       </c>
@@ -18394,7 +18986,7 @@
         <v>5190</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -18477,7 +19069,7 @@
         <v>5191</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -18557,7 +19149,7 @@
         <v>5192</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -18634,7 +19226,7 @@
         <v>5193</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -18711,7 +19303,7 @@
         <v>5194</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>246</v>
       </c>
@@ -18788,7 +19380,7 @@
         <v>5195</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -18865,7 +19457,7 @@
         <v>5196</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>55</v>
       </c>
@@ -18942,7 +19534,7 @@
         <v>5197</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
@@ -19019,7 +19611,7 @@
         <v>5198</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>269</v>
       </c>
@@ -19093,7 +19685,7 @@
         <v>5199</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>270</v>
       </c>
@@ -19167,7 +19759,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
         <v>271</v>
       </c>
@@ -19241,7 +19833,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
         <v>272</v>
       </c>
@@ -19315,7 +19907,7 @@
         <v>5201</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
         <v>273</v>
       </c>
@@ -19389,7 +19981,7 @@
         <v>5202</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
         <v>274</v>
       </c>
@@ -19463,7 +20055,7 @@
         <v>5203</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B30" s="1" t="s">
         <v>275</v>
       </c>
@@ -19537,7 +20129,7 @@
         <v>2755</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
         <v>276</v>
       </c>
@@ -19611,7 +20203,7 @@
         <v>5204</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
         <v>277</v>
       </c>
@@ -19685,7 +20277,7 @@
         <v>5205</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
         <v>278</v>
       </c>
@@ -19759,7 +20351,7 @@
         <v>5206</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
         <v>279</v>
       </c>
@@ -19833,7 +20425,7 @@
         <v>5207</v>
       </c>
     </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
         <v>280</v>
       </c>
@@ -19907,7 +20499,7 @@
         <v>5208</v>
       </c>
     </row>
-    <row r="36" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
         <v>281</v>
       </c>
@@ -19981,7 +20573,7 @@
         <v>3803</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
         <v>282</v>
       </c>
@@ -20052,7 +20644,7 @@
         <v>5209</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
         <v>283</v>
       </c>
@@ -20123,7 +20715,7 @@
         <v>5210</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
         <v>284</v>
       </c>
@@ -20194,7 +20786,7 @@
         <v>5211</v>
       </c>
     </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
         <v>285</v>
       </c>
@@ -20265,7 +20857,7 @@
         <v>5212</v>
       </c>
     </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
         <v>286</v>
       </c>
@@ -20336,7 +20928,7 @@
         <v>5213</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
         <v>287</v>
       </c>
@@ -20407,7 +20999,7 @@
         <v>5214</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
         <v>288</v>
       </c>
@@ -20478,7 +21070,7 @@
         <v>5215</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
         <v>289</v>
       </c>
@@ -20549,7 +21141,7 @@
         <v>5216</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
         <v>290</v>
       </c>
@@ -20620,7 +21212,7 @@
         <v>5217</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
         <v>291</v>
       </c>
@@ -20691,7 +21283,7 @@
         <v>5218</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>292</v>
       </c>
@@ -20762,7 +21354,7 @@
         <v>5219</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
         <v>293</v>
       </c>
@@ -20833,7 +21425,7 @@
         <v>5220</v>
       </c>
     </row>
-    <row r="49" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
         <v>294</v>
       </c>
@@ -20904,7 +21496,7 @@
         <v>5221</v>
       </c>
     </row>
-    <row r="50" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
         <v>295</v>
       </c>
@@ -20975,7 +21567,7 @@
         <v>5222</v>
       </c>
     </row>
-    <row r="51" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>296</v>
       </c>
@@ -21046,7 +21638,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="52" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
         <v>297</v>
       </c>
@@ -21117,7 +21709,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="53" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
         <v>298</v>
       </c>
@@ -21188,7 +21780,7 @@
         <v>5223</v>
       </c>
     </row>
-    <row r="54" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
         <v>299</v>
       </c>
@@ -21256,7 +21848,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="55" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
         <v>300</v>
       </c>
@@ -21324,7 +21916,7 @@
         <v>5224</v>
       </c>
     </row>
-    <row r="56" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
         <v>301</v>
       </c>
@@ -21392,7 +21984,7 @@
         <v>5225</v>
       </c>
     </row>
-    <row r="57" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
         <v>302</v>
       </c>
@@ -21460,7 +22052,7 @@
         <v>5226</v>
       </c>
     </row>
-    <row r="58" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
         <v>303</v>
       </c>
@@ -21528,7 +22120,7 @@
         <v>5227</v>
       </c>
     </row>
-    <row r="59" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
         <v>304</v>
       </c>
@@ -21596,7 +22188,7 @@
         <v>5228</v>
       </c>
     </row>
-    <row r="60" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
         <v>305</v>
       </c>
@@ -21664,7 +22256,7 @@
         <v>5229</v>
       </c>
     </row>
-    <row r="61" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
         <v>306</v>
       </c>
@@ -21732,7 +22324,7 @@
         <v>5230</v>
       </c>
     </row>
-    <row r="62" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
         <v>307</v>
       </c>
@@ -21800,7 +22392,7 @@
         <v>5231</v>
       </c>
     </row>
-    <row r="63" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
         <v>308</v>
       </c>
@@ -21868,7 +22460,7 @@
         <v>5232</v>
       </c>
     </row>
-    <row r="64" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
         <v>309</v>
       </c>
@@ -21933,7 +22525,7 @@
         <v>5233</v>
       </c>
     </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
         <v>310</v>
       </c>
@@ -21998,7 +22590,7 @@
         <v>5234</v>
       </c>
     </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
         <v>311</v>
       </c>
@@ -22063,7 +22655,7 @@
         <v>5235</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
         <v>312</v>
       </c>
@@ -22128,7 +22720,7 @@
         <v>5236</v>
       </c>
     </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
         <v>313</v>
       </c>
@@ -22193,7 +22785,7 @@
         <v>5237</v>
       </c>
     </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
         <v>314</v>
       </c>
@@ -22258,7 +22850,7 @@
         <v>5238</v>
       </c>
     </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
         <v>315</v>
       </c>
@@ -22323,7 +22915,7 @@
         <v>3933</v>
       </c>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
         <v>316</v>
       </c>
@@ -22388,7 +22980,7 @@
         <v>5239</v>
       </c>
     </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B72" s="1" t="s">
         <v>317</v>
       </c>
@@ -22453,7 +23045,7 @@
         <v>5240</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B73" s="1" t="s">
         <v>318</v>
       </c>
@@ -22518,7 +23110,7 @@
         <v>5241</v>
       </c>
     </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B74" s="1" t="s">
         <v>319</v>
       </c>
@@ -22583,7 +23175,7 @@
         <v>5242</v>
       </c>
     </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B75" s="1" t="s">
         <v>320</v>
       </c>
@@ -22648,7 +23240,7 @@
         <v>5243</v>
       </c>
     </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B76" s="1" t="s">
         <v>321</v>
       </c>
@@ -22713,7 +23305,7 @@
         <v>5244</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B77" s="1" t="s">
         <v>322</v>
       </c>
@@ -22775,7 +23367,7 @@
         <v>5245</v>
       </c>
     </row>
-    <row r="78" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
         <v>323</v>
       </c>
@@ -22837,7 +23429,7 @@
         <v>5246</v>
       </c>
     </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B79" s="1" t="s">
         <v>324</v>
       </c>
@@ -22899,7 +23491,7 @@
         <v>5247</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B80" s="1" t="s">
         <v>325</v>
       </c>
@@ -22958,7 +23550,7 @@
         <v>5248</v>
       </c>
     </row>
-    <row r="81" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
         <v>326</v>
       </c>
@@ -23014,7 +23606,7 @@
         <v>5249</v>
       </c>
     </row>
-    <row r="82" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
         <v>327</v>
       </c>
@@ -23070,7 +23662,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="83" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B83" s="1" t="s">
         <v>328</v>
       </c>
@@ -23126,7 +23718,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="84" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
         <v>329</v>
       </c>
@@ -23182,7 +23774,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="85" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B85" s="1" t="s">
         <v>330</v>
       </c>
@@ -23238,7 +23830,7 @@
         <v>5250</v>
       </c>
     </row>
-    <row r="86" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
         <v>331</v>
       </c>
@@ -23294,7 +23886,7 @@
         <v>5251</v>
       </c>
     </row>
-    <row r="87" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B87" s="1" t="s">
         <v>332</v>
       </c>
@@ -23350,7 +23942,7 @@
         <v>5252</v>
       </c>
     </row>
-    <row r="88" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
         <v>333</v>
       </c>
@@ -23406,7 +23998,7 @@
         <v>5253</v>
       </c>
     </row>
-    <row r="89" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
         <v>334</v>
       </c>
@@ -23462,7 +24054,7 @@
         <v>5254</v>
       </c>
     </row>
-    <row r="90" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B90" s="1" t="s">
         <v>335</v>
       </c>
@@ -23518,7 +24110,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="91" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B91" s="1" t="s">
         <v>336</v>
       </c>
@@ -23574,7 +24166,7 @@
         <v>5255</v>
       </c>
     </row>
-    <row r="92" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B92" s="1" t="s">
         <v>337</v>
       </c>
@@ -23630,7 +24222,7 @@
         <v>5256</v>
       </c>
     </row>
-    <row r="93" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
         <v>338</v>
       </c>
@@ -23686,7 +24278,7 @@
         <v>5257</v>
       </c>
     </row>
-    <row r="94" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B94" s="1" t="s">
         <v>339</v>
       </c>
@@ -23739,7 +24331,7 @@
         <v>5258</v>
       </c>
     </row>
-    <row r="95" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B95" s="1" t="s">
         <v>340</v>
       </c>
@@ -23792,7 +24384,7 @@
         <v>5259</v>
       </c>
     </row>
-    <row r="96" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B96" s="1" t="s">
         <v>341</v>
       </c>
@@ -23845,7 +24437,7 @@
         <v>2467</v>
       </c>
     </row>
-    <row r="97" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B97" s="1" t="s">
         <v>342</v>
       </c>
@@ -23898,7 +24490,7 @@
         <v>5260</v>
       </c>
     </row>
-    <row r="98" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B98" s="1" t="s">
         <v>343</v>
       </c>
@@ -23951,7 +24543,7 @@
         <v>5261</v>
       </c>
     </row>
-    <row r="99" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B99" s="1" t="s">
         <v>344</v>
       </c>
@@ -24004,7 +24596,7 @@
         <v>5262</v>
       </c>
     </row>
-    <row r="100" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B100" s="1" t="s">
         <v>345</v>
       </c>
@@ -24057,7 +24649,7 @@
         <v>5263</v>
       </c>
     </row>
-    <row r="101" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B101" s="1" t="s">
         <v>346</v>
       </c>
@@ -24110,7 +24702,7 @@
         <v>5264</v>
       </c>
     </row>
-    <row r="102" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B102" s="1" t="s">
         <v>347</v>
       </c>
@@ -24163,7 +24755,7 @@
         <v>5265</v>
       </c>
     </row>
-    <row r="103" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B103" s="1" t="s">
         <v>348</v>
       </c>
@@ -24216,7 +24808,7 @@
         <v>5266</v>
       </c>
     </row>
-    <row r="104" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E104" s="1" t="s">
         <v>528</v>
       </c>
@@ -24266,7 +24858,7 @@
         <v>5267</v>
       </c>
     </row>
-    <row r="105" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E105" s="1" t="s">
         <v>529</v>
       </c>
@@ -24316,7 +24908,7 @@
         <v>5268</v>
       </c>
     </row>
-    <row r="106" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E106" s="1" t="s">
         <v>530</v>
       </c>
@@ -24366,7 +24958,7 @@
         <v>5269</v>
       </c>
     </row>
-    <row r="107" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E107" s="1" t="s">
         <v>531</v>
       </c>
@@ -24416,7 +25008,7 @@
         <v>5270</v>
       </c>
     </row>
-    <row r="108" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E108" s="1" t="s">
         <v>532</v>
       </c>
@@ -24466,7 +25058,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="109" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E109" s="1" t="s">
         <v>533</v>
       </c>
@@ -24516,7 +25108,7 @@
         <v>5271</v>
       </c>
     </row>
-    <row r="110" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E110" s="1" t="s">
         <v>534</v>
       </c>
@@ -24566,7 +25158,7 @@
         <v>5272</v>
       </c>
     </row>
-    <row r="111" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E111" s="1" t="s">
         <v>535</v>
       </c>
@@ -24616,7 +25208,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="112" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:27" x14ac:dyDescent="0.35">
       <c r="E112" s="1" t="s">
         <v>536</v>
       </c>
@@ -24666,7 +25258,7 @@
         <v>5273</v>
       </c>
     </row>
-    <row r="113" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E113" s="1" t="s">
         <v>537</v>
       </c>
@@ -24716,7 +25308,7 @@
         <v>5274</v>
       </c>
     </row>
-    <row r="114" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E114" s="1" t="s">
         <v>538</v>
       </c>
@@ -24766,7 +25358,7 @@
         <v>5275</v>
       </c>
     </row>
-    <row r="115" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E115" s="1" t="s">
         <v>539</v>
       </c>
@@ -24816,7 +25408,7 @@
         <v>5276</v>
       </c>
     </row>
-    <row r="116" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E116" s="1" t="s">
         <v>540</v>
       </c>
@@ -24866,7 +25458,7 @@
         <v>5277</v>
       </c>
     </row>
-    <row r="117" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E117" s="1" t="s">
         <v>541</v>
       </c>
@@ -24916,7 +25508,7 @@
         <v>5278</v>
       </c>
     </row>
-    <row r="118" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E118" s="1" t="s">
         <v>542</v>
       </c>
@@ -24966,7 +25558,7 @@
         <v>5279</v>
       </c>
     </row>
-    <row r="119" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E119" s="1" t="s">
         <v>543</v>
       </c>
@@ -25016,7 +25608,7 @@
         <v>5280</v>
       </c>
     </row>
-    <row r="120" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E120" s="1" t="s">
         <v>544</v>
       </c>
@@ -25066,7 +25658,7 @@
         <v>5281</v>
       </c>
     </row>
-    <row r="121" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E121" s="1" t="s">
         <v>545</v>
       </c>
@@ -25116,7 +25708,7 @@
         <v>5282</v>
       </c>
     </row>
-    <row r="122" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E122" s="1" t="s">
         <v>546</v>
       </c>
@@ -25166,7 +25758,7 @@
         <v>5283</v>
       </c>
     </row>
-    <row r="123" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E123" s="1" t="s">
         <v>547</v>
       </c>
@@ -25216,7 +25808,7 @@
         <v>5284</v>
       </c>
     </row>
-    <row r="124" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E124" s="1" t="s">
         <v>548</v>
       </c>
@@ -25266,7 +25858,7 @@
         <v>5285</v>
       </c>
     </row>
-    <row r="125" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E125" s="1" t="s">
         <v>549</v>
       </c>
@@ -25316,7 +25908,7 @@
         <v>5286</v>
       </c>
     </row>
-    <row r="126" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E126" s="1" t="s">
         <v>550</v>
       </c>
@@ -25366,7 +25958,7 @@
         <v>5287</v>
       </c>
     </row>
-    <row r="127" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E127" s="1" t="s">
         <v>551</v>
       </c>
@@ -25416,7 +26008,7 @@
         <v>5288</v>
       </c>
     </row>
-    <row r="128" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E128" s="1" t="s">
         <v>552</v>
       </c>
@@ -25466,7 +26058,7 @@
         <v>5289</v>
       </c>
     </row>
-    <row r="129" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E129" s="1" t="s">
         <v>553</v>
       </c>
@@ -25516,7 +26108,7 @@
         <v>5290</v>
       </c>
     </row>
-    <row r="130" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E130" s="1" t="s">
         <v>554</v>
       </c>
@@ -25566,7 +26158,7 @@
         <v>5291</v>
       </c>
     </row>
-    <row r="131" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E131" s="1" t="s">
         <v>555</v>
       </c>
@@ -25616,7 +26208,7 @@
         <v>5292</v>
       </c>
     </row>
-    <row r="132" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E132" s="1" t="s">
         <v>556</v>
       </c>
@@ -25666,7 +26258,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="133" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E133" s="1" t="s">
         <v>557</v>
       </c>
@@ -25716,7 +26308,7 @@
         <v>5293</v>
       </c>
     </row>
-    <row r="134" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="134" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E134" s="1" t="s">
         <v>558</v>
       </c>
@@ -25766,7 +26358,7 @@
         <v>5294</v>
       </c>
     </row>
-    <row r="135" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E135" s="1" t="s">
         <v>559</v>
       </c>
@@ -25816,7 +26408,7 @@
         <v>5295</v>
       </c>
     </row>
-    <row r="136" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E136" s="1" t="s">
         <v>560</v>
       </c>
@@ -25866,7 +26458,7 @@
         <v>5296</v>
       </c>
     </row>
-    <row r="137" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="137" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E137" s="1" t="s">
         <v>561</v>
       </c>
@@ -25916,7 +26508,7 @@
         <v>5297</v>
       </c>
     </row>
-    <row r="138" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="138" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E138" s="1" t="s">
         <v>562</v>
       </c>
@@ -25966,7 +26558,7 @@
         <v>5298</v>
       </c>
     </row>
-    <row r="139" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E139" s="1" t="s">
         <v>563</v>
       </c>
@@ -26016,7 +26608,7 @@
         <v>5299</v>
       </c>
     </row>
-    <row r="140" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E140" s="1" t="s">
         <v>564</v>
       </c>
@@ -26066,7 +26658,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="141" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E141" s="1" t="s">
         <v>565</v>
       </c>
@@ -26113,7 +26705,7 @@
         <v>4646</v>
       </c>
     </row>
-    <row r="142" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E142" s="1" t="s">
         <v>566</v>
       </c>
@@ -26157,7 +26749,7 @@
         <v>4647</v>
       </c>
     </row>
-    <row r="143" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="143" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E143" s="1" t="s">
         <v>567</v>
       </c>
@@ -26201,7 +26793,7 @@
         <v>4648</v>
       </c>
     </row>
-    <row r="144" spans="5:27" x14ac:dyDescent="0.25">
+    <row r="144" spans="5:27" x14ac:dyDescent="0.35">
       <c r="E144" s="1" t="s">
         <v>568</v>
       </c>
@@ -26245,7 +26837,7 @@
         <v>4649</v>
       </c>
     </row>
-    <row r="145" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E145" s="1" t="s">
         <v>569</v>
       </c>
@@ -26286,7 +26878,7 @@
         <v>4650</v>
       </c>
     </row>
-    <row r="146" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E146" s="1" t="s">
         <v>570</v>
       </c>
@@ -26327,7 +26919,7 @@
         <v>4651</v>
       </c>
     </row>
-    <row r="147" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E147" s="1" t="s">
         <v>571</v>
       </c>
@@ -26368,7 +26960,7 @@
         <v>4652</v>
       </c>
     </row>
-    <row r="148" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E148" s="1" t="s">
         <v>572</v>
       </c>
@@ -26409,7 +27001,7 @@
         <v>4653</v>
       </c>
     </row>
-    <row r="149" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E149" s="1" t="s">
         <v>573</v>
       </c>
@@ -26450,7 +27042,7 @@
         <v>4654</v>
       </c>
     </row>
-    <row r="150" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E150" s="1" t="s">
         <v>574</v>
       </c>
@@ -26491,7 +27083,7 @@
         <v>4655</v>
       </c>
     </row>
-    <row r="151" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E151" s="1" t="s">
         <v>575</v>
       </c>
@@ -26532,7 +27124,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="152" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E152" s="1" t="s">
         <v>576</v>
       </c>
@@ -26573,7 +27165,7 @@
         <v>4656</v>
       </c>
     </row>
-    <row r="153" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E153" s="1" t="s">
         <v>577</v>
       </c>
@@ -26614,7 +27206,7 @@
         <v>4657</v>
       </c>
     </row>
-    <row r="154" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E154" s="1" t="s">
         <v>578</v>
       </c>
@@ -26655,7 +27247,7 @@
         <v>4658</v>
       </c>
     </row>
-    <row r="155" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E155" s="1" t="s">
         <v>579</v>
       </c>
@@ -26696,7 +27288,7 @@
         <v>4659</v>
       </c>
     </row>
-    <row r="156" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E156" s="1" t="s">
         <v>580</v>
       </c>
@@ -26737,7 +27329,7 @@
         <v>4660</v>
       </c>
     </row>
-    <row r="157" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E157" s="1" t="s">
         <v>581</v>
       </c>
@@ -26778,7 +27370,7 @@
         <v>4661</v>
       </c>
     </row>
-    <row r="158" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E158" s="1" t="s">
         <v>582</v>
       </c>
@@ -26819,7 +27411,7 @@
         <v>4662</v>
       </c>
     </row>
-    <row r="159" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E159" s="1" t="s">
         <v>583</v>
       </c>
@@ -26860,7 +27452,7 @@
         <v>4663</v>
       </c>
     </row>
-    <row r="160" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E160" s="1" t="s">
         <v>584</v>
       </c>
@@ -26901,7 +27493,7 @@
         <v>4664</v>
       </c>
     </row>
-    <row r="161" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E161" s="1" t="s">
         <v>585</v>
       </c>
@@ -26942,7 +27534,7 @@
         <v>4665</v>
       </c>
     </row>
-    <row r="162" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E162" s="1" t="s">
         <v>586</v>
       </c>
@@ -26983,7 +27575,7 @@
         <v>4666</v>
       </c>
     </row>
-    <row r="163" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E163" s="1" t="s">
         <v>587</v>
       </c>
@@ -27024,7 +27616,7 @@
         <v>4667</v>
       </c>
     </row>
-    <row r="164" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E164" s="1" t="s">
         <v>588</v>
       </c>
@@ -27065,7 +27657,7 @@
         <v>4668</v>
       </c>
     </row>
-    <row r="165" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E165" s="1" t="s">
         <v>589</v>
       </c>
@@ -27106,7 +27698,7 @@
         <v>4669</v>
       </c>
     </row>
-    <row r="166" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E166" s="1" t="s">
         <v>590</v>
       </c>
@@ -27147,7 +27739,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="167" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E167" s="1" t="s">
         <v>591</v>
       </c>
@@ -27188,7 +27780,7 @@
         <v>4670</v>
       </c>
     </row>
-    <row r="168" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E168" s="1" t="s">
         <v>592</v>
       </c>
@@ -27229,7 +27821,7 @@
         <v>4671</v>
       </c>
     </row>
-    <row r="169" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E169" s="1" t="s">
         <v>593</v>
       </c>
@@ -27270,7 +27862,7 @@
         <v>4672</v>
       </c>
     </row>
-    <row r="170" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E170" s="1" t="s">
         <v>594</v>
       </c>
@@ -27308,7 +27900,7 @@
         <v>4673</v>
       </c>
     </row>
-    <row r="171" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E171" s="1" t="s">
         <v>595</v>
       </c>
@@ -27346,7 +27938,7 @@
         <v>4674</v>
       </c>
     </row>
-    <row r="172" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E172" s="1" t="s">
         <v>596</v>
       </c>
@@ -27384,7 +27976,7 @@
         <v>4675</v>
       </c>
     </row>
-    <row r="173" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="173" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E173" s="1" t="s">
         <v>597</v>
       </c>
@@ -27422,7 +28014,7 @@
         <v>4676</v>
       </c>
     </row>
-    <row r="174" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="174" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E174" s="1" t="s">
         <v>598</v>
       </c>
@@ -27460,7 +28052,7 @@
         <v>4677</v>
       </c>
     </row>
-    <row r="175" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E175" s="1" t="s">
         <v>599</v>
       </c>
@@ -27498,7 +28090,7 @@
         <v>4678</v>
       </c>
     </row>
-    <row r="176" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="176" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E176" s="1" t="s">
         <v>600</v>
       </c>
@@ -27536,7 +28128,7 @@
         <v>4679</v>
       </c>
     </row>
-    <row r="177" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="177" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E177" s="1" t="s">
         <v>601</v>
       </c>
@@ -27574,7 +28166,7 @@
         <v>4680</v>
       </c>
     </row>
-    <row r="178" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="178" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E178" s="1" t="s">
         <v>602</v>
       </c>
@@ -27612,7 +28204,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="179" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="179" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E179" s="1" t="s">
         <v>603</v>
       </c>
@@ -27650,7 +28242,7 @@
         <v>4681</v>
       </c>
     </row>
-    <row r="180" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="180" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E180" s="1" t="s">
         <v>604</v>
       </c>
@@ -27688,7 +28280,7 @@
         <v>4682</v>
       </c>
     </row>
-    <row r="181" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="181" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E181" s="1" t="s">
         <v>605</v>
       </c>
@@ -27726,7 +28318,7 @@
         <v>4683</v>
       </c>
     </row>
-    <row r="182" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="182" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E182" s="1" t="s">
         <v>606</v>
       </c>
@@ -27764,7 +28356,7 @@
         <v>4684</v>
       </c>
     </row>
-    <row r="183" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="183" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E183" s="1" t="s">
         <v>607</v>
       </c>
@@ -27802,7 +28394,7 @@
         <v>4685</v>
       </c>
     </row>
-    <row r="184" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="184" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E184" s="1" t="s">
         <v>608</v>
       </c>
@@ -27840,7 +28432,7 @@
         <v>4686</v>
       </c>
     </row>
-    <row r="185" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="185" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E185" s="1" t="s">
         <v>609</v>
       </c>
@@ -27878,7 +28470,7 @@
         <v>4687</v>
       </c>
     </row>
-    <row r="186" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="186" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E186" s="1" t="s">
         <v>610</v>
       </c>
@@ -27913,7 +28505,7 @@
         <v>4688</v>
       </c>
     </row>
-    <row r="187" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="187" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E187" s="1" t="s">
         <v>611</v>
       </c>
@@ -27945,7 +28537,7 @@
         <v>4689</v>
       </c>
     </row>
-    <row r="188" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="188" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E188" s="1" t="s">
         <v>612</v>
       </c>
@@ -27977,7 +28569,7 @@
         <v>4690</v>
       </c>
     </row>
-    <row r="189" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="189" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E189" s="1" t="s">
         <v>613</v>
       </c>
@@ -28009,7 +28601,7 @@
         <v>4691</v>
       </c>
     </row>
-    <row r="190" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="190" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E190" s="1" t="s">
         <v>614</v>
       </c>
@@ -28041,7 +28633,7 @@
         <v>4692</v>
       </c>
     </row>
-    <row r="191" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="191" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E191" s="1" t="s">
         <v>615</v>
       </c>
@@ -28073,7 +28665,7 @@
         <v>4693</v>
       </c>
     </row>
-    <row r="192" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="192" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E192" s="1" t="s">
         <v>616</v>
       </c>
@@ -28105,7 +28697,7 @@
         <v>4694</v>
       </c>
     </row>
-    <row r="193" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="193" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E193" s="1" t="s">
         <v>617</v>
       </c>
@@ -28137,7 +28729,7 @@
         <v>4695</v>
       </c>
     </row>
-    <row r="194" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="194" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E194" s="1" t="s">
         <v>618</v>
       </c>
@@ -28169,7 +28761,7 @@
         <v>4696</v>
       </c>
     </row>
-    <row r="195" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="195" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E195" s="1" t="s">
         <v>619</v>
       </c>
@@ -28201,7 +28793,7 @@
         <v>4697</v>
       </c>
     </row>
-    <row r="196" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="196" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E196" s="1" t="s">
         <v>620</v>
       </c>
@@ -28233,7 +28825,7 @@
         <v>4698</v>
       </c>
     </row>
-    <row r="197" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="197" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E197" s="1" t="s">
         <v>621</v>
       </c>
@@ -28265,7 +28857,7 @@
         <v>4699</v>
       </c>
     </row>
-    <row r="198" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="198" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E198" s="1" t="s">
         <v>622</v>
       </c>
@@ -28297,7 +28889,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="199" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="199" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E199" s="1" t="s">
         <v>623</v>
       </c>
@@ -28329,7 +28921,7 @@
         <v>4701</v>
       </c>
     </row>
-    <row r="200" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="200" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E200" s="1" t="s">
         <v>624</v>
       </c>
@@ -28361,7 +28953,7 @@
         <v>4702</v>
       </c>
     </row>
-    <row r="201" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="201" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E201" s="1" t="s">
         <v>625</v>
       </c>
@@ -28393,7 +28985,7 @@
         <v>4703</v>
       </c>
     </row>
-    <row r="202" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="202" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E202" s="1" t="s">
         <v>626</v>
       </c>
@@ -28425,7 +29017,7 @@
         <v>3013</v>
       </c>
     </row>
-    <row r="203" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="203" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E203" s="1" t="s">
         <v>627</v>
       </c>
@@ -28457,7 +29049,7 @@
         <v>4704</v>
       </c>
     </row>
-    <row r="204" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="204" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E204" s="1" t="s">
         <v>628</v>
       </c>
@@ -28489,7 +29081,7 @@
         <v>4705</v>
       </c>
     </row>
-    <row r="205" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="205" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E205" s="1" t="s">
         <v>629</v>
       </c>
@@ -28521,7 +29113,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="206" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="206" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E206" s="1" t="s">
         <v>630</v>
       </c>
@@ -28553,7 +29145,7 @@
         <v>4706</v>
       </c>
     </row>
-    <row r="207" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="207" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E207" s="1" t="s">
         <v>631</v>
       </c>
@@ -28585,7 +29177,7 @@
         <v>3018</v>
       </c>
     </row>
-    <row r="208" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="208" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E208" s="1" t="s">
         <v>632</v>
       </c>
@@ -28617,7 +29209,7 @@
         <v>4707</v>
       </c>
     </row>
-    <row r="209" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="209" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E209" s="1" t="s">
         <v>633</v>
       </c>
@@ -28649,7 +29241,7 @@
         <v>4708</v>
       </c>
     </row>
-    <row r="210" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="210" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E210" s="1" t="s">
         <v>634</v>
       </c>
@@ -28681,7 +29273,7 @@
         <v>4709</v>
       </c>
     </row>
-    <row r="211" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="211" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E211" s="1" t="s">
         <v>635</v>
       </c>
@@ -28713,7 +29305,7 @@
         <v>4710</v>
       </c>
     </row>
-    <row r="212" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="212" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E212" s="1" t="s">
         <v>636</v>
       </c>
@@ -28745,7 +29337,7 @@
         <v>4711</v>
       </c>
     </row>
-    <row r="213" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="213" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E213" s="1" t="s">
         <v>637</v>
       </c>
@@ -28777,7 +29369,7 @@
         <v>4712</v>
       </c>
     </row>
-    <row r="214" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="214" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E214" s="1" t="s">
         <v>638</v>
       </c>
@@ -28809,7 +29401,7 @@
         <v>4713</v>
       </c>
     </row>
-    <row r="215" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="215" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E215" s="1" t="s">
         <v>639</v>
       </c>
@@ -28841,7 +29433,7 @@
         <v>4714</v>
       </c>
     </row>
-    <row r="216" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="216" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E216" s="1" t="s">
         <v>640</v>
       </c>
@@ -28873,7 +29465,7 @@
         <v>4715</v>
       </c>
     </row>
-    <row r="217" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="217" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E217" s="1" t="s">
         <v>641</v>
       </c>
@@ -28905,7 +29497,7 @@
         <v>4716</v>
       </c>
     </row>
-    <row r="218" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="218" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E218" s="1" t="s">
         <v>642</v>
       </c>
@@ -28937,7 +29529,7 @@
         <v>4717</v>
       </c>
     </row>
-    <row r="219" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="219" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E219" s="1" t="s">
         <v>643</v>
       </c>
@@ -28966,7 +29558,7 @@
         <v>4718</v>
       </c>
     </row>
-    <row r="220" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="220" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E220" s="1" t="s">
         <v>644</v>
       </c>
@@ -28995,7 +29587,7 @@
         <v>4719</v>
       </c>
     </row>
-    <row r="221" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="221" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E221" s="1" t="s">
         <v>645</v>
       </c>
@@ -29024,7 +29616,7 @@
         <v>4720</v>
       </c>
     </row>
-    <row r="222" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="222" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E222" s="1" t="s">
         <v>646</v>
       </c>
@@ -29053,7 +29645,7 @@
         <v>4721</v>
       </c>
     </row>
-    <row r="223" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="223" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E223" s="1" t="s">
         <v>647</v>
       </c>
@@ -29082,7 +29674,7 @@
         <v>4722</v>
       </c>
     </row>
-    <row r="224" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="224" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E224" s="1" t="s">
         <v>648</v>
       </c>
@@ -29108,7 +29700,7 @@
         <v>4723</v>
       </c>
     </row>
-    <row r="225" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="225" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E225" s="1" t="s">
         <v>649</v>
       </c>
@@ -29134,7 +29726,7 @@
         <v>4724</v>
       </c>
     </row>
-    <row r="226" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="226" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E226" s="1" t="s">
         <v>650</v>
       </c>
@@ -29157,7 +29749,7 @@
         <v>4725</v>
       </c>
     </row>
-    <row r="227" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="227" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E227" s="1" t="s">
         <v>651</v>
       </c>
@@ -29180,7 +29772,7 @@
         <v>4726</v>
       </c>
     </row>
-    <row r="228" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="228" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E228" s="1" t="s">
         <v>652</v>
       </c>
@@ -29203,7 +29795,7 @@
         <v>4727</v>
       </c>
     </row>
-    <row r="229" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="229" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E229" s="1" t="s">
         <v>653</v>
       </c>
@@ -29226,7 +29818,7 @@
         <v>4728</v>
       </c>
     </row>
-    <row r="230" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="230" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E230" s="1" t="s">
         <v>654</v>
       </c>
@@ -29249,7 +29841,7 @@
         <v>4729</v>
       </c>
     </row>
-    <row r="231" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="231" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E231" s="1" t="s">
         <v>655</v>
       </c>
@@ -29272,7 +29864,7 @@
         <v>4730</v>
       </c>
     </row>
-    <row r="232" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="232" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E232" s="1" t="s">
         <v>656</v>
       </c>
@@ -29295,7 +29887,7 @@
         <v>4731</v>
       </c>
     </row>
-    <row r="233" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="233" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E233" s="1" t="s">
         <v>657</v>
       </c>
@@ -29318,7 +29910,7 @@
         <v>4732</v>
       </c>
     </row>
-    <row r="234" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="234" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E234" s="1" t="s">
         <v>658</v>
       </c>
@@ -29341,7 +29933,7 @@
         <v>4733</v>
       </c>
     </row>
-    <row r="235" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="235" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E235" s="1" t="s">
         <v>659</v>
       </c>
@@ -29364,7 +29956,7 @@
         <v>4734</v>
       </c>
     </row>
-    <row r="236" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="236" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E236" s="1" t="s">
         <v>660</v>
       </c>
@@ -29387,7 +29979,7 @@
         <v>4735</v>
       </c>
     </row>
-    <row r="237" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="237" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E237" s="1" t="s">
         <v>661</v>
       </c>
@@ -29410,7 +30002,7 @@
         <v>4736</v>
       </c>
     </row>
-    <row r="238" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="238" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E238" s="1" t="s">
         <v>662</v>
       </c>
@@ -29433,7 +30025,7 @@
         <v>4737</v>
       </c>
     </row>
-    <row r="239" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="239" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E239" s="1" t="s">
         <v>663</v>
       </c>
@@ -29456,7 +30048,7 @@
         <v>4738</v>
       </c>
     </row>
-    <row r="240" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="240" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E240" s="1" t="s">
         <v>664</v>
       </c>
@@ -29479,7 +30071,7 @@
         <v>4739</v>
       </c>
     </row>
-    <row r="241" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="241" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E241" s="1" t="s">
         <v>665</v>
       </c>
@@ -29502,7 +30094,7 @@
         <v>4740</v>
       </c>
     </row>
-    <row r="242" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="242" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E242" s="1" t="s">
         <v>666</v>
       </c>
@@ -29525,7 +30117,7 @@
         <v>4741</v>
       </c>
     </row>
-    <row r="243" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="243" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E243" s="1" t="s">
         <v>667</v>
       </c>
@@ -29548,7 +30140,7 @@
         <v>4742</v>
       </c>
     </row>
-    <row r="244" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="244" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E244" s="1" t="s">
         <v>668</v>
       </c>
@@ -29571,7 +30163,7 @@
         <v>4743</v>
       </c>
     </row>
-    <row r="245" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="245" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E245" s="1" t="s">
         <v>669</v>
       </c>
@@ -29594,7 +30186,7 @@
         <v>4744</v>
       </c>
     </row>
-    <row r="246" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="246" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E246" s="1" t="s">
         <v>670</v>
       </c>
@@ -29617,7 +30209,7 @@
         <v>4745</v>
       </c>
     </row>
-    <row r="247" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="247" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E247" s="1" t="s">
         <v>671</v>
       </c>
@@ -29640,7 +30232,7 @@
         <v>4746</v>
       </c>
     </row>
-    <row r="248" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="248" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E248" s="1" t="s">
         <v>672</v>
       </c>
@@ -29660,7 +30252,7 @@
         <v>4747</v>
       </c>
     </row>
-    <row r="249" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="249" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E249" s="1" t="s">
         <v>673</v>
       </c>
@@ -29680,7 +30272,7 @@
         <v>4748</v>
       </c>
     </row>
-    <row r="250" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="250" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E250" s="1" t="s">
         <v>674</v>
       </c>
@@ -29700,7 +30292,7 @@
         <v>4749</v>
       </c>
     </row>
-    <row r="251" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="251" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E251" s="1" t="s">
         <v>675</v>
       </c>
@@ -29720,7 +30312,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="252" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="252" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E252" s="1" t="s">
         <v>676</v>
       </c>
@@ -29740,7 +30332,7 @@
         <v>4751</v>
       </c>
     </row>
-    <row r="253" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="253" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E253" s="1" t="s">
         <v>677</v>
       </c>
@@ -29760,7 +30352,7 @@
         <v>4752</v>
       </c>
     </row>
-    <row r="254" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="254" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E254" s="1" t="s">
         <v>678</v>
       </c>
@@ -29780,7 +30372,7 @@
         <v>4753</v>
       </c>
     </row>
-    <row r="255" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="255" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E255" s="1" t="s">
         <v>679</v>
       </c>
@@ -29800,7 +30392,7 @@
         <v>4754</v>
       </c>
     </row>
-    <row r="256" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="256" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E256" s="1" t="s">
         <v>680</v>
       </c>
@@ -29820,7 +30412,7 @@
         <v>4755</v>
       </c>
     </row>
-    <row r="257" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="257" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E257" s="1" t="s">
         <v>681</v>
       </c>
@@ -29840,7 +30432,7 @@
         <v>4756</v>
       </c>
     </row>
-    <row r="258" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="258" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E258" s="1" t="s">
         <v>682</v>
       </c>
@@ -29860,7 +30452,7 @@
         <v>4757</v>
       </c>
     </row>
-    <row r="259" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="259" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E259" s="1" t="s">
         <v>683</v>
       </c>
@@ -29880,7 +30472,7 @@
         <v>4758</v>
       </c>
     </row>
-    <row r="260" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="260" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E260" s="1" t="s">
         <v>684</v>
       </c>
@@ -29900,7 +30492,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="261" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="261" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E261" s="1" t="s">
         <v>685</v>
       </c>
@@ -29920,7 +30512,7 @@
         <v>4759</v>
       </c>
     </row>
-    <row r="262" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="262" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E262" s="1" t="s">
         <v>686</v>
       </c>
@@ -29940,7 +30532,7 @@
         <v>4760</v>
       </c>
     </row>
-    <row r="263" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="263" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E263" s="1" t="s">
         <v>687</v>
       </c>
@@ -29960,7 +30552,7 @@
         <v>4761</v>
       </c>
     </row>
-    <row r="264" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="264" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E264" s="1" t="s">
         <v>688</v>
       </c>
@@ -29980,7 +30572,7 @@
         <v>4762</v>
       </c>
     </row>
-    <row r="265" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="265" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E265" s="1" t="s">
         <v>689</v>
       </c>
@@ -30000,7 +30592,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="266" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="266" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E266" s="1" t="s">
         <v>690</v>
       </c>
@@ -30020,7 +30612,7 @@
         <v>4763</v>
       </c>
     </row>
-    <row r="267" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="267" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E267" s="1" t="s">
         <v>691</v>
       </c>
@@ -30040,7 +30632,7 @@
         <v>4764</v>
       </c>
     </row>
-    <row r="268" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="268" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E268" s="1" t="s">
         <v>692</v>
       </c>
@@ -30060,7 +30652,7 @@
         <v>4765</v>
       </c>
     </row>
-    <row r="269" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="269" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E269" s="1" t="s">
         <v>693</v>
       </c>
@@ -30080,7 +30672,7 @@
         <v>4766</v>
       </c>
     </row>
-    <row r="270" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="270" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E270" s="1" t="s">
         <v>694</v>
       </c>
@@ -30100,7 +30692,7 @@
         <v>4767</v>
       </c>
     </row>
-    <row r="271" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="271" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E271" s="1" t="s">
         <v>695</v>
       </c>
@@ -30120,7 +30712,7 @@
         <v>4768</v>
       </c>
     </row>
-    <row r="272" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="272" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E272" s="1" t="s">
         <v>696</v>
       </c>
@@ -30140,7 +30732,7 @@
         <v>4769</v>
       </c>
     </row>
-    <row r="273" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="273" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E273" s="1" t="s">
         <v>697</v>
       </c>
@@ -30160,7 +30752,7 @@
         <v>4770</v>
       </c>
     </row>
-    <row r="274" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="274" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E274" s="1" t="s">
         <v>698</v>
       </c>
@@ -30180,7 +30772,7 @@
         <v>4771</v>
       </c>
     </row>
-    <row r="275" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="275" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E275" s="1" t="s">
         <v>699</v>
       </c>
@@ -30200,7 +30792,7 @@
         <v>4772</v>
       </c>
     </row>
-    <row r="276" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="276" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E276" s="1" t="s">
         <v>700</v>
       </c>
@@ -30220,7 +30812,7 @@
         <v>4773</v>
       </c>
     </row>
-    <row r="277" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="277" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E277" s="1" t="s">
         <v>701</v>
       </c>
@@ -30240,7 +30832,7 @@
         <v>4774</v>
       </c>
     </row>
-    <row r="278" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="278" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E278" s="1" t="s">
         <v>702</v>
       </c>
@@ -30260,7 +30852,7 @@
         <v>4775</v>
       </c>
     </row>
-    <row r="279" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="279" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E279" s="1" t="s">
         <v>703</v>
       </c>
@@ -30280,7 +30872,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="280" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="280" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E280" s="1" t="s">
         <v>704</v>
       </c>
@@ -30300,7 +30892,7 @@
         <v>4776</v>
       </c>
     </row>
-    <row r="281" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="281" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E281" s="1" t="s">
         <v>705</v>
       </c>
@@ -30320,7 +30912,7 @@
         <v>4777</v>
       </c>
     </row>
-    <row r="282" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="282" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E282" s="1" t="s">
         <v>706</v>
       </c>
@@ -30340,7 +30932,7 @@
         <v>4778</v>
       </c>
     </row>
-    <row r="283" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="283" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E283" s="1" t="s">
         <v>707</v>
       </c>
@@ -30360,7 +30952,7 @@
         <v>4779</v>
       </c>
     </row>
-    <row r="284" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="284" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E284" s="1" t="s">
         <v>708</v>
       </c>
@@ -30380,7 +30972,7 @@
         <v>4780</v>
       </c>
     </row>
-    <row r="285" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="285" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E285" s="1" t="s">
         <v>709</v>
       </c>
@@ -30400,7 +30992,7 @@
         <v>4781</v>
       </c>
     </row>
-    <row r="286" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="286" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E286" s="1" t="s">
         <v>710</v>
       </c>
@@ -30420,7 +31012,7 @@
         <v>4782</v>
       </c>
     </row>
-    <row r="287" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="287" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E287" s="1" t="s">
         <v>711</v>
       </c>
@@ -30440,7 +31032,7 @@
         <v>4783</v>
       </c>
     </row>
-    <row r="288" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="288" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E288" s="1" t="s">
         <v>712</v>
       </c>
@@ -30460,7 +31052,7 @@
         <v>4373</v>
       </c>
     </row>
-    <row r="289" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="289" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E289" s="1" t="s">
         <v>713</v>
       </c>
@@ -30480,7 +31072,7 @@
         <v>4784</v>
       </c>
     </row>
-    <row r="290" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="290" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E290" s="1" t="s">
         <v>714</v>
       </c>
@@ -30500,7 +31092,7 @@
         <v>4785</v>
       </c>
     </row>
-    <row r="291" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="291" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E291" s="1" t="s">
         <v>715</v>
       </c>
@@ -30520,7 +31112,7 @@
         <v>4786</v>
       </c>
     </row>
-    <row r="292" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="292" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E292" s="1" t="s">
         <v>716</v>
       </c>
@@ -30540,7 +31132,7 @@
         <v>4787</v>
       </c>
     </row>
-    <row r="293" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="293" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E293" s="1" t="s">
         <v>717</v>
       </c>
@@ -30560,7 +31152,7 @@
         <v>4788</v>
       </c>
     </row>
-    <row r="294" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="294" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E294" s="1" t="s">
         <v>718</v>
       </c>
@@ -30580,7 +31172,7 @@
         <v>4789</v>
       </c>
     </row>
-    <row r="295" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="295" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E295" s="1" t="s">
         <v>719</v>
       </c>
@@ -30597,7 +31189,7 @@
         <v>4790</v>
       </c>
     </row>
-    <row r="296" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="296" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E296" s="1" t="s">
         <v>720</v>
       </c>
@@ -30614,7 +31206,7 @@
         <v>4791</v>
       </c>
     </row>
-    <row r="297" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="297" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E297" s="1" t="s">
         <v>721</v>
       </c>
@@ -30631,7 +31223,7 @@
         <v>4792</v>
       </c>
     </row>
-    <row r="298" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="298" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E298" s="1" t="s">
         <v>722</v>
       </c>
@@ -30648,7 +31240,7 @@
         <v>4793</v>
       </c>
     </row>
-    <row r="299" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="299" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E299" s="1" t="s">
         <v>723</v>
       </c>
@@ -30665,7 +31257,7 @@
         <v>4794</v>
       </c>
     </row>
-    <row r="300" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="300" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E300" s="1" t="s">
         <v>724</v>
       </c>
@@ -30682,7 +31274,7 @@
         <v>4795</v>
       </c>
     </row>
-    <row r="301" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="301" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E301" s="1" t="s">
         <v>725</v>
       </c>
@@ -30699,7 +31291,7 @@
         <v>4796</v>
       </c>
     </row>
-    <row r="302" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="302" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E302" s="1" t="s">
         <v>726</v>
       </c>
@@ -30716,7 +31308,7 @@
         <v>4797</v>
       </c>
     </row>
-    <row r="303" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="303" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E303" s="1" t="s">
         <v>727</v>
       </c>
@@ -30733,7 +31325,7 @@
         <v>4798</v>
       </c>
     </row>
-    <row r="304" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="304" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E304" s="1" t="s">
         <v>728</v>
       </c>
@@ -30750,7 +31342,7 @@
         <v>4799</v>
       </c>
     </row>
-    <row r="305" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="305" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E305" s="1" t="s">
         <v>729</v>
       </c>
@@ -30767,7 +31359,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="306" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="306" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E306" s="1" t="s">
         <v>730</v>
       </c>
@@ -30784,7 +31376,7 @@
         <v>4801</v>
       </c>
     </row>
-    <row r="307" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="307" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E307" s="1" t="s">
         <v>731</v>
       </c>
@@ -30801,7 +31393,7 @@
         <v>4802</v>
       </c>
     </row>
-    <row r="308" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="308" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E308" s="1" t="s">
         <v>732</v>
       </c>
@@ -30818,7 +31410,7 @@
         <v>4803</v>
       </c>
     </row>
-    <row r="309" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="309" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E309" s="1" t="s">
         <v>733</v>
       </c>
@@ -30835,7 +31427,7 @@
         <v>4804</v>
       </c>
     </row>
-    <row r="310" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="310" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E310" s="1" t="s">
         <v>734</v>
       </c>
@@ -30852,7 +31444,7 @@
         <v>4805</v>
       </c>
     </row>
-    <row r="311" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="311" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E311" s="1" t="s">
         <v>735</v>
       </c>
@@ -30869,7 +31461,7 @@
         <v>4806</v>
       </c>
     </row>
-    <row r="312" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="312" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E312" s="1" t="s">
         <v>736</v>
       </c>
@@ -30886,7 +31478,7 @@
         <v>4807</v>
       </c>
     </row>
-    <row r="313" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="313" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E313" s="1" t="s">
         <v>737</v>
       </c>
@@ -30903,7 +31495,7 @@
         <v>4808</v>
       </c>
     </row>
-    <row r="314" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="314" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E314" s="1" t="s">
         <v>738</v>
       </c>
@@ -30920,7 +31512,7 @@
         <v>4809</v>
       </c>
     </row>
-    <row r="315" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="315" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E315" s="1" t="s">
         <v>739</v>
       </c>
@@ -30937,7 +31529,7 @@
         <v>4810</v>
       </c>
     </row>
-    <row r="316" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="316" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E316" s="1" t="s">
         <v>740</v>
       </c>
@@ -30954,7 +31546,7 @@
         <v>4811</v>
       </c>
     </row>
-    <row r="317" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="317" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E317" s="1" t="s">
         <v>741</v>
       </c>
@@ -30971,7 +31563,7 @@
         <v>4812</v>
       </c>
     </row>
-    <row r="318" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="318" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E318" s="1" t="s">
         <v>742</v>
       </c>
@@ -30988,7 +31580,7 @@
         <v>4813</v>
       </c>
     </row>
-    <row r="319" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="319" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E319" s="1" t="s">
         <v>743</v>
       </c>
@@ -31005,7 +31597,7 @@
         <v>4814</v>
       </c>
     </row>
-    <row r="320" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="320" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E320" s="1" t="s">
         <v>744</v>
       </c>
@@ -31022,7 +31614,7 @@
         <v>4815</v>
       </c>
     </row>
-    <row r="321" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="321" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E321" s="1" t="s">
         <v>745</v>
       </c>
@@ -31039,7 +31631,7 @@
         <v>4816</v>
       </c>
     </row>
-    <row r="322" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="322" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E322" s="1" t="s">
         <v>746</v>
       </c>
@@ -31056,7 +31648,7 @@
         <v>4817</v>
       </c>
     </row>
-    <row r="323" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="323" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E323" s="1" t="s">
         <v>747</v>
       </c>
@@ -31073,7 +31665,7 @@
         <v>4818</v>
       </c>
     </row>
-    <row r="324" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="324" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E324" s="1" t="s">
         <v>748</v>
       </c>
@@ -31090,7 +31682,7 @@
         <v>4819</v>
       </c>
     </row>
-    <row r="325" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="325" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E325" s="1" t="s">
         <v>749</v>
       </c>
@@ -31107,7 +31699,7 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="326" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="326" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E326" s="1" t="s">
         <v>750</v>
       </c>
@@ -31124,7 +31716,7 @@
         <v>4821</v>
       </c>
     </row>
-    <row r="327" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="327" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E327" s="1" t="s">
         <v>751</v>
       </c>
@@ -31141,7 +31733,7 @@
         <v>4822</v>
       </c>
     </row>
-    <row r="328" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="328" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E328" s="1" t="s">
         <v>752</v>
       </c>
@@ -31158,7 +31750,7 @@
         <v>4823</v>
       </c>
     </row>
-    <row r="329" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="329" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E329" s="1" t="s">
         <v>753</v>
       </c>
@@ -31175,7 +31767,7 @@
         <v>4824</v>
       </c>
     </row>
-    <row r="330" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="330" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E330" s="1" t="s">
         <v>754</v>
       </c>
@@ -31192,7 +31784,7 @@
         <v>4825</v>
       </c>
     </row>
-    <row r="331" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="331" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E331" s="1" t="s">
         <v>755</v>
       </c>
@@ -31209,7 +31801,7 @@
         <v>4826</v>
       </c>
     </row>
-    <row r="332" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="332" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E332" s="1" t="s">
         <v>756</v>
       </c>
@@ -31226,7 +31818,7 @@
         <v>4827</v>
       </c>
     </row>
-    <row r="333" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="333" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E333" s="1" t="s">
         <v>757</v>
       </c>
@@ -31243,7 +31835,7 @@
         <v>4828</v>
       </c>
     </row>
-    <row r="334" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="334" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E334" s="1" t="s">
         <v>758</v>
       </c>
@@ -31260,7 +31852,7 @@
         <v>4829</v>
       </c>
     </row>
-    <row r="335" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="335" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E335" s="1" t="s">
         <v>759</v>
       </c>
@@ -31277,7 +31869,7 @@
         <v>4830</v>
       </c>
     </row>
-    <row r="336" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="336" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E336" s="1" t="s">
         <v>760</v>
       </c>
@@ -31294,7 +31886,7 @@
         <v>4831</v>
       </c>
     </row>
-    <row r="337" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="337" spans="5:25" x14ac:dyDescent="0.35">
       <c r="E337" s="1" t="s">
         <v>761</v>
       </c>
@@ -31311,7 +31903,7 @@
         <v>4832</v>
       </c>
     </row>
-    <row r="338" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="338" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M338" s="1" t="s">
         <v>1870</v>
       </c>
@@ -31325,7 +31917,7 @@
         <v>4833</v>
       </c>
     </row>
-    <row r="339" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="339" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M339" s="1" t="s">
         <v>1871</v>
       </c>
@@ -31339,7 +31931,7 @@
         <v>4834</v>
       </c>
     </row>
-    <row r="340" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="340" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M340" s="1" t="s">
         <v>1872</v>
       </c>
@@ -31353,7 +31945,7 @@
         <v>4835</v>
       </c>
     </row>
-    <row r="341" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="341" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M341" s="1" t="s">
         <v>1873</v>
       </c>
@@ -31367,7 +31959,7 @@
         <v>4836</v>
       </c>
     </row>
-    <row r="342" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="342" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M342" s="1" t="s">
         <v>1874</v>
       </c>
@@ -31381,7 +31973,7 @@
         <v>4837</v>
       </c>
     </row>
-    <row r="343" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="343" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M343" s="1" t="s">
         <v>1875</v>
       </c>
@@ -31395,7 +31987,7 @@
         <v>4838</v>
       </c>
     </row>
-    <row r="344" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="344" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M344" s="1" t="s">
         <v>1876</v>
       </c>
@@ -31409,7 +32001,7 @@
         <v>4839</v>
       </c>
     </row>
-    <row r="345" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="345" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M345" s="1" t="s">
         <v>1877</v>
       </c>
@@ -31423,7 +32015,7 @@
         <v>4840</v>
       </c>
     </row>
-    <row r="346" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="346" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M346" s="1" t="s">
         <v>1878</v>
       </c>
@@ -31437,7 +32029,7 @@
         <v>4841</v>
       </c>
     </row>
-    <row r="347" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="347" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M347" s="1" t="s">
         <v>1879</v>
       </c>
@@ -31451,7 +32043,7 @@
         <v>4842</v>
       </c>
     </row>
-    <row r="348" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="348" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M348" s="1" t="s">
         <v>1880</v>
       </c>
@@ -31465,7 +32057,7 @@
         <v>4843</v>
       </c>
     </row>
-    <row r="349" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="349" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M349" s="1" t="s">
         <v>1881</v>
       </c>
@@ -31479,7 +32071,7 @@
         <v>4844</v>
       </c>
     </row>
-    <row r="350" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="350" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M350" s="1" t="s">
         <v>1882</v>
       </c>
@@ -31493,7 +32085,7 @@
         <v>4845</v>
       </c>
     </row>
-    <row r="351" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="351" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M351" s="1" t="s">
         <v>1883</v>
       </c>
@@ -31507,7 +32099,7 @@
         <v>4846</v>
       </c>
     </row>
-    <row r="352" spans="5:25" x14ac:dyDescent="0.25">
+    <row r="352" spans="5:25" x14ac:dyDescent="0.35">
       <c r="M352" s="1" t="s">
         <v>1884</v>
       </c>
@@ -31521,7 +32113,7 @@
         <v>4847</v>
       </c>
     </row>
-    <row r="353" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="353" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M353" s="1" t="s">
         <v>1885</v>
       </c>
@@ -31535,7 +32127,7 @@
         <v>4848</v>
       </c>
     </row>
-    <row r="354" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="354" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M354" s="1" t="s">
         <v>1886</v>
       </c>
@@ -31549,7 +32141,7 @@
         <v>4849</v>
       </c>
     </row>
-    <row r="355" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="355" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M355" s="1" t="s">
         <v>1887</v>
       </c>
@@ -31563,7 +32155,7 @@
         <v>4850</v>
       </c>
     </row>
-    <row r="356" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="356" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M356" s="1" t="s">
         <v>1888</v>
       </c>
@@ -31577,7 +32169,7 @@
         <v>4851</v>
       </c>
     </row>
-    <row r="357" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="357" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M357" s="1" t="s">
         <v>1889</v>
       </c>
@@ -31591,7 +32183,7 @@
         <v>4402</v>
       </c>
     </row>
-    <row r="358" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="358" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M358" s="1" t="s">
         <v>1890</v>
       </c>
@@ -31605,7 +32197,7 @@
         <v>4852</v>
       </c>
     </row>
-    <row r="359" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="359" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M359" s="1" t="s">
         <v>1891</v>
       </c>
@@ -31619,7 +32211,7 @@
         <v>4853</v>
       </c>
     </row>
-    <row r="360" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="360" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M360" s="1" t="s">
         <v>1892</v>
       </c>
@@ -31633,7 +32225,7 @@
         <v>4854</v>
       </c>
     </row>
-    <row r="361" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="361" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M361" s="1" t="s">
         <v>1893</v>
       </c>
@@ -31647,7 +32239,7 @@
         <v>4855</v>
       </c>
     </row>
-    <row r="362" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="362" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M362" s="1" t="s">
         <v>1894</v>
       </c>
@@ -31661,7 +32253,7 @@
         <v>4856</v>
       </c>
     </row>
-    <row r="363" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="363" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M363" s="1" t="s">
         <v>1895</v>
       </c>
@@ -31675,7 +32267,7 @@
         <v>4857</v>
       </c>
     </row>
-    <row r="364" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="364" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M364" s="1" t="s">
         <v>1896</v>
       </c>
@@ -31689,7 +32281,7 @@
         <v>4858</v>
       </c>
     </row>
-    <row r="365" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="365" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M365" s="1" t="s">
         <v>1897</v>
       </c>
@@ -31703,7 +32295,7 @@
         <v>4859</v>
       </c>
     </row>
-    <row r="366" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="366" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M366" s="1" t="s">
         <v>1898</v>
       </c>
@@ -31717,7 +32309,7 @@
         <v>4860</v>
       </c>
     </row>
-    <row r="367" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="367" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M367" s="1" t="s">
         <v>1899</v>
       </c>
@@ -31731,7 +32323,7 @@
         <v>4861</v>
       </c>
     </row>
-    <row r="368" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="368" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M368" s="1" t="s">
         <v>1900</v>
       </c>
@@ -31745,7 +32337,7 @@
         <v>4862</v>
       </c>
     </row>
-    <row r="369" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="369" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M369" s="1" t="s">
         <v>1901</v>
       </c>
@@ -31759,7 +32351,7 @@
         <v>4863</v>
       </c>
     </row>
-    <row r="370" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="370" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M370" s="1" t="s">
         <v>1902</v>
       </c>
@@ -31773,7 +32365,7 @@
         <v>4864</v>
       </c>
     </row>
-    <row r="371" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="371" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M371" s="1" t="s">
         <v>1903</v>
       </c>
@@ -31787,7 +32379,7 @@
         <v>4865</v>
       </c>
     </row>
-    <row r="372" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="372" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M372" s="1" t="s">
         <v>1904</v>
       </c>
@@ -31801,7 +32393,7 @@
         <v>4866</v>
       </c>
     </row>
-    <row r="373" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="373" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M373" s="1" t="s">
         <v>1905</v>
       </c>
@@ -31815,7 +32407,7 @@
         <v>4867</v>
       </c>
     </row>
-    <row r="374" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="374" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M374" s="1" t="s">
         <v>1906</v>
       </c>
@@ -31829,7 +32421,7 @@
         <v>4868</v>
       </c>
     </row>
-    <row r="375" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="375" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M375" s="1" t="s">
         <v>1907</v>
       </c>
@@ -31843,7 +32435,7 @@
         <v>4869</v>
       </c>
     </row>
-    <row r="376" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="376" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M376" s="1" t="s">
         <v>1908</v>
       </c>
@@ -31857,7 +32449,7 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="377" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="377" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M377" s="1" t="s">
         <v>1909</v>
       </c>
@@ -31871,7 +32463,7 @@
         <v>4871</v>
       </c>
     </row>
-    <row r="378" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="378" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M378" s="1" t="s">
         <v>1910</v>
       </c>
@@ -31885,7 +32477,7 @@
         <v>4872</v>
       </c>
     </row>
-    <row r="379" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="379" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M379" s="1" t="s">
         <v>1911</v>
       </c>
@@ -31899,7 +32491,7 @@
         <v>4873</v>
       </c>
     </row>
-    <row r="380" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="380" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M380" s="1" t="s">
         <v>1912</v>
       </c>
@@ -31913,7 +32505,7 @@
         <v>4874</v>
       </c>
     </row>
-    <row r="381" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="381" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M381" s="1" t="s">
         <v>1913</v>
       </c>
@@ -31927,7 +32519,7 @@
         <v>4875</v>
       </c>
     </row>
-    <row r="382" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="382" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M382" s="1" t="s">
         <v>1914</v>
       </c>
@@ -31941,7 +32533,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="383" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="383" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M383" s="1" t="s">
         <v>1915</v>
       </c>
@@ -31955,7 +32547,7 @@
         <v>4876</v>
       </c>
     </row>
-    <row r="384" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="384" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M384" s="1" t="s">
         <v>1916</v>
       </c>
@@ -31969,7 +32561,7 @@
         <v>4877</v>
       </c>
     </row>
-    <row r="385" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="385" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M385" s="1" t="s">
         <v>1917</v>
       </c>
@@ -31983,7 +32575,7 @@
         <v>4878</v>
       </c>
     </row>
-    <row r="386" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="386" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M386" s="1" t="s">
         <v>1918</v>
       </c>
@@ -31997,7 +32589,7 @@
         <v>4879</v>
       </c>
     </row>
-    <row r="387" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="387" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M387" s="1" t="s">
         <v>1919</v>
       </c>
@@ -32011,7 +32603,7 @@
         <v>4880</v>
       </c>
     </row>
-    <row r="388" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="388" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M388" s="1" t="s">
         <v>1920</v>
       </c>
@@ -32025,7 +32617,7 @@
         <v>4881</v>
       </c>
     </row>
-    <row r="389" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="389" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M389" s="1" t="s">
         <v>1921</v>
       </c>
@@ -32039,7 +32631,7 @@
         <v>4882</v>
       </c>
     </row>
-    <row r="390" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="390" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M390" s="1" t="s">
         <v>1922</v>
       </c>
@@ -32053,7 +32645,7 @@
         <v>4883</v>
       </c>
     </row>
-    <row r="391" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="391" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M391" s="1" t="s">
         <v>1923</v>
       </c>
@@ -32067,7 +32659,7 @@
         <v>4884</v>
       </c>
     </row>
-    <row r="392" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="392" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M392" s="1" t="s">
         <v>1924</v>
       </c>
@@ -32081,7 +32673,7 @@
         <v>4885</v>
       </c>
     </row>
-    <row r="393" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="393" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M393" s="1" t="s">
         <v>1925</v>
       </c>
@@ -32095,7 +32687,7 @@
         <v>4886</v>
       </c>
     </row>
-    <row r="394" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="394" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M394" s="1" t="s">
         <v>1926</v>
       </c>
@@ -32109,7 +32701,7 @@
         <v>4887</v>
       </c>
     </row>
-    <row r="395" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="395" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M395" s="1" t="s">
         <v>1927</v>
       </c>
@@ -32123,7 +32715,7 @@
         <v>4412</v>
       </c>
     </row>
-    <row r="396" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="396" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M396" s="1" t="s">
         <v>1928</v>
       </c>
@@ -32137,7 +32729,7 @@
         <v>4888</v>
       </c>
     </row>
-    <row r="397" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="397" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M397" s="1" t="s">
         <v>1929</v>
       </c>
@@ -32151,7 +32743,7 @@
         <v>4889</v>
       </c>
     </row>
-    <row r="398" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="398" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M398" s="1" t="s">
         <v>1930</v>
       </c>
@@ -32165,7 +32757,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="399" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="399" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M399" s="1" t="s">
         <v>1931</v>
       </c>
@@ -32179,7 +32771,7 @@
         <v>4890</v>
       </c>
     </row>
-    <row r="400" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="400" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M400" s="1" t="s">
         <v>1932</v>
       </c>
@@ -32193,7 +32785,7 @@
         <v>4891</v>
       </c>
     </row>
-    <row r="401" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="401" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M401" s="1" t="s">
         <v>1933</v>
       </c>
@@ -32204,7 +32796,7 @@
         <v>3124</v>
       </c>
     </row>
-    <row r="402" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="402" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M402" s="1" t="s">
         <v>1934</v>
       </c>
@@ -32215,7 +32807,7 @@
         <v>4892</v>
       </c>
     </row>
-    <row r="403" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="403" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M403" s="1" t="s">
         <v>1935</v>
       </c>
@@ -32226,7 +32818,7 @@
         <v>4893</v>
       </c>
     </row>
-    <row r="404" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="404" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M404" s="1" t="s">
         <v>1936</v>
       </c>
@@ -32237,7 +32829,7 @@
         <v>4894</v>
       </c>
     </row>
-    <row r="405" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="405" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M405" s="1" t="s">
         <v>1937</v>
       </c>
@@ -32248,7 +32840,7 @@
         <v>4419</v>
       </c>
     </row>
-    <row r="406" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="406" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M406" s="1" t="s">
         <v>1938</v>
       </c>
@@ -32259,7 +32851,7 @@
         <v>4895</v>
       </c>
     </row>
-    <row r="407" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="407" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M407" s="1" t="s">
         <v>1939</v>
       </c>
@@ -32270,7 +32862,7 @@
         <v>4896</v>
       </c>
     </row>
-    <row r="408" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="408" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M408" s="1" t="s">
         <v>1940</v>
       </c>
@@ -32281,7 +32873,7 @@
         <v>4897</v>
       </c>
     </row>
-    <row r="409" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="409" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M409" s="1" t="s">
         <v>1941</v>
       </c>
@@ -32292,7 +32884,7 @@
         <v>4898</v>
       </c>
     </row>
-    <row r="410" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="410" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M410" s="1" t="s">
         <v>1942</v>
       </c>
@@ -32303,7 +32895,7 @@
         <v>4899</v>
       </c>
     </row>
-    <row r="411" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="411" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M411" s="1" t="s">
         <v>1943</v>
       </c>
@@ -32314,7 +32906,7 @@
         <v>4900</v>
       </c>
     </row>
-    <row r="412" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="412" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M412" s="1" t="s">
         <v>1944</v>
       </c>
@@ -32325,7 +32917,7 @@
         <v>4901</v>
       </c>
     </row>
-    <row r="413" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="413" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M413" s="1" t="s">
         <v>1945</v>
       </c>
@@ -32336,7 +32928,7 @@
         <v>4902</v>
       </c>
     </row>
-    <row r="414" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="414" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M414" s="1" t="s">
         <v>1946</v>
       </c>
@@ -32347,7 +32939,7 @@
         <v>4903</v>
       </c>
     </row>
-    <row r="415" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="415" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M415" s="1" t="s">
         <v>1947</v>
       </c>
@@ -32358,7 +32950,7 @@
         <v>4904</v>
       </c>
     </row>
-    <row r="416" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="416" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M416" s="1" t="s">
         <v>1948</v>
       </c>
@@ -32369,7 +32961,7 @@
         <v>4905</v>
       </c>
     </row>
-    <row r="417" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="417" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M417" s="1" t="s">
         <v>1949</v>
       </c>
@@ -32380,7 +32972,7 @@
         <v>4906</v>
       </c>
     </row>
-    <row r="418" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="418" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M418" s="1" t="s">
         <v>1950</v>
       </c>
@@ -32391,7 +32983,7 @@
         <v>4907</v>
       </c>
     </row>
-    <row r="419" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="419" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M419" s="1" t="s">
         <v>1951</v>
       </c>
@@ -32402,7 +32994,7 @@
         <v>4908</v>
       </c>
     </row>
-    <row r="420" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="420" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M420" s="1" t="s">
         <v>1952</v>
       </c>
@@ -32413,7 +33005,7 @@
         <v>4909</v>
       </c>
     </row>
-    <row r="421" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="421" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M421" s="1" t="s">
         <v>1953</v>
       </c>
@@ -32424,7 +33016,7 @@
         <v>4910</v>
       </c>
     </row>
-    <row r="422" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="422" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M422" s="1" t="s">
         <v>1954</v>
       </c>
@@ -32435,7 +33027,7 @@
         <v>4911</v>
       </c>
     </row>
-    <row r="423" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="423" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M423" s="1" t="s">
         <v>1955</v>
       </c>
@@ -32446,7 +33038,7 @@
         <v>4912</v>
       </c>
     </row>
-    <row r="424" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="424" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M424" s="1" t="s">
         <v>1956</v>
       </c>
@@ -32457,7 +33049,7 @@
         <v>4913</v>
       </c>
     </row>
-    <row r="425" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="425" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M425" s="1" t="s">
         <v>1957</v>
       </c>
@@ -32468,7 +33060,7 @@
         <v>4914</v>
       </c>
     </row>
-    <row r="426" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="426" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M426" s="1" t="s">
         <v>1958</v>
       </c>
@@ -32479,7 +33071,7 @@
         <v>4915</v>
       </c>
     </row>
-    <row r="427" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="427" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M427" s="1" t="s">
         <v>1959</v>
       </c>
@@ -32490,7 +33082,7 @@
         <v>4916</v>
       </c>
     </row>
-    <row r="428" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="428" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M428" s="1" t="s">
         <v>1960</v>
       </c>
@@ -32501,7 +33093,7 @@
         <v>4917</v>
       </c>
     </row>
-    <row r="429" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="429" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M429" s="1" t="s">
         <v>1961</v>
       </c>
@@ -32512,7 +33104,7 @@
         <v>4918</v>
       </c>
     </row>
-    <row r="430" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="430" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M430" s="1" t="s">
         <v>1962</v>
       </c>
@@ -32523,7 +33115,7 @@
         <v>4919</v>
       </c>
     </row>
-    <row r="431" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="431" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M431" s="1" t="s">
         <v>1963</v>
       </c>
@@ -32534,7 +33126,7 @@
         <v>4920</v>
       </c>
     </row>
-    <row r="432" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="432" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M432" s="1" t="s">
         <v>1003</v>
       </c>
@@ -32545,7 +33137,7 @@
         <v>4921</v>
       </c>
     </row>
-    <row r="433" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="433" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M433" s="1" t="s">
         <v>1964</v>
       </c>
@@ -32556,7 +33148,7 @@
         <v>4426</v>
       </c>
     </row>
-    <row r="434" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="434" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M434" s="1" t="s">
         <v>1965</v>
       </c>
@@ -32567,7 +33159,7 @@
         <v>4922</v>
       </c>
     </row>
-    <row r="435" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="435" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M435" s="1" t="s">
         <v>1966</v>
       </c>
@@ -32578,7 +33170,7 @@
         <v>4923</v>
       </c>
     </row>
-    <row r="436" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="436" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M436" s="1" t="s">
         <v>1967</v>
       </c>
@@ -32589,7 +33181,7 @@
         <v>4924</v>
       </c>
     </row>
-    <row r="437" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="437" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M437" s="1" t="s">
         <v>1968</v>
       </c>
@@ -32600,7 +33192,7 @@
         <v>4925</v>
       </c>
     </row>
-    <row r="438" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="438" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M438" s="1" t="s">
         <v>1969</v>
       </c>
@@ -32611,7 +33203,7 @@
         <v>4926</v>
       </c>
     </row>
-    <row r="439" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="439" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M439" s="1" t="s">
         <v>1970</v>
       </c>
@@ -32622,7 +33214,7 @@
         <v>4927</v>
       </c>
     </row>
-    <row r="440" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="440" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M440" s="1" t="s">
         <v>1971</v>
       </c>
@@ -32633,7 +33225,7 @@
         <v>4928</v>
       </c>
     </row>
-    <row r="441" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="441" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M441" s="1" t="s">
         <v>1972</v>
       </c>
@@ -32644,7 +33236,7 @@
         <v>4929</v>
       </c>
     </row>
-    <row r="442" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="442" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M442" s="1" t="s">
         <v>1973</v>
       </c>
@@ -32655,7 +33247,7 @@
         <v>4930</v>
       </c>
     </row>
-    <row r="443" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="443" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M443" s="1" t="s">
         <v>1974</v>
       </c>
@@ -32666,7 +33258,7 @@
         <v>4931</v>
       </c>
     </row>
-    <row r="444" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="444" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M444" s="1" t="s">
         <v>1975</v>
       </c>
@@ -32677,7 +33269,7 @@
         <v>4932</v>
       </c>
     </row>
-    <row r="445" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="445" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M445" s="1" t="s">
         <v>1976</v>
       </c>
@@ -32688,7 +33280,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="446" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="446" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M446" s="1" t="s">
         <v>1977</v>
       </c>
@@ -32699,7 +33291,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="447" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="447" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M447" s="1" t="s">
         <v>1978</v>
       </c>
@@ -32710,7 +33302,7 @@
         <v>4933</v>
       </c>
     </row>
-    <row r="448" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="448" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M448" s="1" t="s">
         <v>1979</v>
       </c>
@@ -32721,7 +33313,7 @@
         <v>4934</v>
       </c>
     </row>
-    <row r="449" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="449" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M449" s="1" t="s">
         <v>1980</v>
       </c>
@@ -32732,7 +33324,7 @@
         <v>4935</v>
       </c>
     </row>
-    <row r="450" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="450" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M450" s="1" t="s">
         <v>1981</v>
       </c>
@@ -32743,7 +33335,7 @@
         <v>4936</v>
       </c>
     </row>
-    <row r="451" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="451" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M451" s="1" t="s">
         <v>1982</v>
       </c>
@@ -32754,7 +33346,7 @@
         <v>4937</v>
       </c>
     </row>
-    <row r="452" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="452" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M452" s="1" t="s">
         <v>1983</v>
       </c>
@@ -32765,7 +33357,7 @@
         <v>4938</v>
       </c>
     </row>
-    <row r="453" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="453" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M453" s="1" t="s">
         <v>1984</v>
       </c>
@@ -32776,7 +33368,7 @@
         <v>4939</v>
       </c>
     </row>
-    <row r="454" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="454" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M454" s="1" t="s">
         <v>1985</v>
       </c>
@@ -32787,7 +33379,7 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="455" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="455" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M455" s="1" t="s">
         <v>1986</v>
       </c>
@@ -32798,7 +33390,7 @@
         <v>4941</v>
       </c>
     </row>
-    <row r="456" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="456" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M456" s="1" t="s">
         <v>1987</v>
       </c>
@@ -32809,7 +33401,7 @@
         <v>4942</v>
       </c>
     </row>
-    <row r="457" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="457" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M457" s="1" t="s">
         <v>1988</v>
       </c>
@@ -32820,7 +33412,7 @@
         <v>4943</v>
       </c>
     </row>
-    <row r="458" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="458" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M458" s="1" t="s">
         <v>1989</v>
       </c>
@@ -32831,7 +33423,7 @@
         <v>4944</v>
       </c>
     </row>
-    <row r="459" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="459" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M459" s="1" t="s">
         <v>1990</v>
       </c>
@@ -32842,7 +33434,7 @@
         <v>4945</v>
       </c>
     </row>
-    <row r="460" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="460" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M460" s="1" t="s">
         <v>1991</v>
       </c>
@@ -32853,7 +33445,7 @@
         <v>4946</v>
       </c>
     </row>
-    <row r="461" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="461" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M461" s="1" t="s">
         <v>1992</v>
       </c>
@@ -32864,7 +33456,7 @@
         <v>4947</v>
       </c>
     </row>
-    <row r="462" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="462" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M462" s="1" t="s">
         <v>1993</v>
       </c>
@@ -32875,7 +33467,7 @@
         <v>4948</v>
       </c>
     </row>
-    <row r="463" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="463" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M463" s="1" t="s">
         <v>1994</v>
       </c>
@@ -32886,7 +33478,7 @@
         <v>4437</v>
       </c>
     </row>
-    <row r="464" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="464" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M464" s="1" t="s">
         <v>1995</v>
       </c>
@@ -32897,7 +33489,7 @@
         <v>4949</v>
       </c>
     </row>
-    <row r="465" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="465" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M465" s="1" t="s">
         <v>1996</v>
       </c>
@@ -32908,7 +33500,7 @@
         <v>4950</v>
       </c>
     </row>
-    <row r="466" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="466" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M466" s="1" t="s">
         <v>1997</v>
       </c>
@@ -32919,7 +33511,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="467" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="467" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M467" s="1" t="s">
         <v>1998</v>
       </c>
@@ -32930,7 +33522,7 @@
         <v>4951</v>
       </c>
     </row>
-    <row r="468" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="468" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M468" s="1" t="s">
         <v>1999</v>
       </c>
@@ -32941,7 +33533,7 @@
         <v>4952</v>
       </c>
     </row>
-    <row r="469" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="469" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M469" s="1" t="s">
         <v>2000</v>
       </c>
@@ -32952,7 +33544,7 @@
         <v>4953</v>
       </c>
     </row>
-    <row r="470" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="470" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M470" s="1" t="s">
         <v>2001</v>
       </c>
@@ -32963,7 +33555,7 @@
         <v>4954</v>
       </c>
     </row>
-    <row r="471" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="471" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M471" s="1" t="s">
         <v>2002</v>
       </c>
@@ -32974,7 +33566,7 @@
         <v>4955</v>
       </c>
     </row>
-    <row r="472" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="472" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M472" s="1" t="s">
         <v>2003</v>
       </c>
@@ -32985,7 +33577,7 @@
         <v>4956</v>
       </c>
     </row>
-    <row r="473" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="473" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M473" s="1" t="s">
         <v>2004</v>
       </c>
@@ -32996,7 +33588,7 @@
         <v>4957</v>
       </c>
     </row>
-    <row r="474" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="474" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M474" s="1" t="s">
         <v>2005</v>
       </c>
@@ -33007,7 +33599,7 @@
         <v>4958</v>
       </c>
     </row>
-    <row r="475" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="475" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M475" s="1" t="s">
         <v>2006</v>
       </c>
@@ -33018,7 +33610,7 @@
         <v>4959</v>
       </c>
     </row>
-    <row r="476" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="476" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M476" s="1" t="s">
         <v>2007</v>
       </c>
@@ -33029,7 +33621,7 @@
         <v>4960</v>
       </c>
     </row>
-    <row r="477" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="477" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M477" s="1" t="s">
         <v>2008</v>
       </c>
@@ -33040,7 +33632,7 @@
         <v>4961</v>
       </c>
     </row>
-    <row r="478" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="478" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M478" s="1" t="s">
         <v>2009</v>
       </c>
@@ -33051,7 +33643,7 @@
         <v>4962</v>
       </c>
     </row>
-    <row r="479" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="479" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M479" s="1" t="s">
         <v>2010</v>
       </c>
@@ -33062,7 +33654,7 @@
         <v>4963</v>
       </c>
     </row>
-    <row r="480" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="480" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M480" s="1" t="s">
         <v>2011</v>
       </c>
@@ -33073,7 +33665,7 @@
         <v>4964</v>
       </c>
     </row>
-    <row r="481" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="481" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M481" s="1" t="s">
         <v>2012</v>
       </c>
@@ -33084,7 +33676,7 @@
         <v>4965</v>
       </c>
     </row>
-    <row r="482" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="482" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M482" s="1" t="s">
         <v>2013</v>
       </c>
@@ -33095,7 +33687,7 @@
         <v>4966</v>
       </c>
     </row>
-    <row r="483" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="483" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M483" s="1" t="s">
         <v>2014</v>
       </c>
@@ -33106,7 +33698,7 @@
         <v>4967</v>
       </c>
     </row>
-    <row r="484" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="484" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M484" s="1" t="s">
         <v>2015</v>
       </c>
@@ -33117,7 +33709,7 @@
         <v>4968</v>
       </c>
     </row>
-    <row r="485" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="485" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M485" s="1" t="s">
         <v>2016</v>
       </c>
@@ -33128,7 +33720,7 @@
         <v>4969</v>
       </c>
     </row>
-    <row r="486" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="486" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M486" s="1" t="s">
         <v>2017</v>
       </c>
@@ -33139,7 +33731,7 @@
         <v>4970</v>
       </c>
     </row>
-    <row r="487" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="487" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M487" s="1" t="s">
         <v>2018</v>
       </c>
@@ -33150,7 +33742,7 @@
         <v>4971</v>
       </c>
     </row>
-    <row r="488" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="488" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M488" s="1" t="s">
         <v>2019</v>
       </c>
@@ -33161,7 +33753,7 @@
         <v>4972</v>
       </c>
     </row>
-    <row r="489" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="489" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M489" s="1" t="s">
         <v>2020</v>
       </c>
@@ -33172,7 +33764,7 @@
         <v>4973</v>
       </c>
     </row>
-    <row r="490" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="490" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M490" s="1" t="s">
         <v>2021</v>
       </c>
@@ -33183,7 +33775,7 @@
         <v>4974</v>
       </c>
     </row>
-    <row r="491" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="491" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M491" s="1" t="s">
         <v>2022</v>
       </c>
@@ -33194,7 +33786,7 @@
         <v>4975</v>
       </c>
     </row>
-    <row r="492" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="492" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M492" s="1" t="s">
         <v>2023</v>
       </c>
@@ -33205,7 +33797,7 @@
         <v>4976</v>
       </c>
     </row>
-    <row r="493" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="493" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M493" s="1" t="s">
         <v>2024</v>
       </c>
@@ -33216,7 +33808,7 @@
         <v>4977</v>
       </c>
     </row>
-    <row r="494" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="494" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M494" s="1" t="s">
         <v>2025</v>
       </c>
@@ -33227,7 +33819,7 @@
         <v>4978</v>
       </c>
     </row>
-    <row r="495" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="495" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M495" s="1" t="s">
         <v>2026</v>
       </c>
@@ -33238,7 +33830,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="496" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="496" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M496" s="1" t="s">
         <v>2027</v>
       </c>
@@ -33249,7 +33841,7 @@
         <v>4979</v>
       </c>
     </row>
-    <row r="497" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="497" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M497" s="1" t="s">
         <v>2028</v>
       </c>
@@ -33260,7 +33852,7 @@
         <v>4980</v>
       </c>
     </row>
-    <row r="498" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="498" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M498" s="1" t="s">
         <v>2029</v>
       </c>
@@ -33271,7 +33863,7 @@
         <v>4981</v>
       </c>
     </row>
-    <row r="499" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="499" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M499" s="1" t="s">
         <v>2030</v>
       </c>
@@ -33279,7 +33871,7 @@
         <v>4982</v>
       </c>
     </row>
-    <row r="500" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="500" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M500" s="1" t="s">
         <v>2031</v>
       </c>
@@ -33287,7 +33879,7 @@
         <v>4983</v>
       </c>
     </row>
-    <row r="501" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="501" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M501" s="1" t="s">
         <v>2032</v>
       </c>
@@ -33295,7 +33887,7 @@
         <v>4984</v>
       </c>
     </row>
-    <row r="502" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="502" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M502" s="1" t="s">
         <v>2033</v>
       </c>
@@ -33303,7 +33895,7 @@
         <v>4985</v>
       </c>
     </row>
-    <row r="503" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="503" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M503" s="1" t="s">
         <v>2034</v>
       </c>
@@ -33311,7 +33903,7 @@
         <v>4986</v>
       </c>
     </row>
-    <row r="504" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="504" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M504" s="1" t="s">
         <v>2035</v>
       </c>
@@ -33319,7 +33911,7 @@
         <v>4987</v>
       </c>
     </row>
-    <row r="505" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="505" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M505" s="1" t="s">
         <v>2036</v>
       </c>
@@ -33327,7 +33919,7 @@
         <v>4988</v>
       </c>
     </row>
-    <row r="506" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="506" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M506" s="1" t="s">
         <v>2037</v>
       </c>
@@ -33335,7 +33927,7 @@
         <v>4989</v>
       </c>
     </row>
-    <row r="507" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="507" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M507" s="1" t="s">
         <v>2038</v>
       </c>
@@ -33343,7 +33935,7 @@
         <v>4990</v>
       </c>
     </row>
-    <row r="508" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="508" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M508" s="1" t="s">
         <v>2039</v>
       </c>
@@ -33351,7 +33943,7 @@
         <v>4991</v>
       </c>
     </row>
-    <row r="509" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="509" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M509" s="1" t="s">
         <v>2040</v>
       </c>
@@ -33359,7 +33951,7 @@
         <v>4992</v>
       </c>
     </row>
-    <row r="510" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="510" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M510" s="1" t="s">
         <v>2041</v>
       </c>
@@ -33367,7 +33959,7 @@
         <v>4455</v>
       </c>
     </row>
-    <row r="511" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="511" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M511" s="1" t="s">
         <v>2042</v>
       </c>
@@ -33375,7 +33967,7 @@
         <v>4993</v>
       </c>
     </row>
-    <row r="512" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="512" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M512" s="1" t="s">
         <v>2043</v>
       </c>
@@ -33383,7 +33975,7 @@
         <v>4994</v>
       </c>
     </row>
-    <row r="513" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="513" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M513" s="1" t="s">
         <v>2044</v>
       </c>
@@ -33391,7 +33983,7 @@
         <v>4995</v>
       </c>
     </row>
-    <row r="514" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="514" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M514" s="1" t="s">
         <v>2045</v>
       </c>
@@ -33399,7 +33991,7 @@
         <v>4996</v>
       </c>
     </row>
-    <row r="515" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="515" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M515" s="1" t="s">
         <v>2046</v>
       </c>
@@ -33407,7 +33999,7 @@
         <v>4997</v>
       </c>
     </row>
-    <row r="516" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="516" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M516" s="1" t="s">
         <v>2047</v>
       </c>
@@ -33415,7 +34007,7 @@
         <v>4998</v>
       </c>
     </row>
-    <row r="517" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="517" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M517" s="1" t="s">
         <v>2048</v>
       </c>
@@ -33423,7 +34015,7 @@
         <v>4999</v>
       </c>
     </row>
-    <row r="518" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="518" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M518" s="1" t="s">
         <v>2049</v>
       </c>
@@ -33431,7 +34023,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="519" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="519" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M519" s="1" t="s">
         <v>2050</v>
       </c>
@@ -33439,7 +34031,7 @@
         <v>5001</v>
       </c>
     </row>
-    <row r="520" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="520" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M520" s="1" t="s">
         <v>2051</v>
       </c>
@@ -33447,7 +34039,7 @@
         <v>5002</v>
       </c>
     </row>
-    <row r="521" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="521" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M521" s="1" t="s">
         <v>2052</v>
       </c>
@@ -33455,7 +34047,7 @@
         <v>5003</v>
       </c>
     </row>
-    <row r="522" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="522" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M522" s="1" t="s">
         <v>2053</v>
       </c>
@@ -33463,7 +34055,7 @@
         <v>5004</v>
       </c>
     </row>
-    <row r="523" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="523" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M523" s="1" t="s">
         <v>2054</v>
       </c>
@@ -33471,7 +34063,7 @@
         <v>5005</v>
       </c>
     </row>
-    <row r="524" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="524" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M524" s="1" t="s">
         <v>2055</v>
       </c>
@@ -33479,7 +34071,7 @@
         <v>5006</v>
       </c>
     </row>
-    <row r="525" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="525" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M525" s="1" t="s">
         <v>2056</v>
       </c>
@@ -33487,7 +34079,7 @@
         <v>5007</v>
       </c>
     </row>
-    <row r="526" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="526" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M526" s="1" t="s">
         <v>2057</v>
       </c>
@@ -33495,7 +34087,7 @@
         <v>5008</v>
       </c>
     </row>
-    <row r="527" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="527" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M527" s="1" t="s">
         <v>2058</v>
       </c>
@@ -33503,7 +34095,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="528" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="528" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M528" s="1" t="s">
         <v>1951</v>
       </c>
@@ -33511,7 +34103,7 @@
         <v>3198</v>
       </c>
     </row>
-    <row r="529" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="529" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M529" s="1" t="s">
         <v>2059</v>
       </c>
@@ -33519,7 +34111,7 @@
         <v>5009</v>
       </c>
     </row>
-    <row r="530" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="530" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M530" s="1" t="s">
         <v>2060</v>
       </c>
@@ -33527,7 +34119,7 @@
         <v>5010</v>
       </c>
     </row>
-    <row r="531" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="531" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M531" s="1" t="s">
         <v>2061</v>
       </c>
@@ -33535,7 +34127,7 @@
         <v>5011</v>
       </c>
     </row>
-    <row r="532" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="532" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M532" s="1" t="s">
         <v>2062</v>
       </c>
@@ -33543,7 +34135,7 @@
         <v>5012</v>
       </c>
     </row>
-    <row r="533" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="533" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M533" s="1" t="s">
         <v>2063</v>
       </c>
@@ -33551,7 +34143,7 @@
         <v>5013</v>
       </c>
     </row>
-    <row r="534" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="534" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M534" s="1" t="s">
         <v>2064</v>
       </c>
@@ -33559,7 +34151,7 @@
         <v>5014</v>
       </c>
     </row>
-    <row r="535" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="535" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M535" s="1" t="s">
         <v>2065</v>
       </c>
@@ -33567,7 +34159,7 @@
         <v>5015</v>
       </c>
     </row>
-    <row r="536" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="536" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M536" s="1" t="s">
         <v>2066</v>
       </c>
@@ -33575,7 +34167,7 @@
         <v>5016</v>
       </c>
     </row>
-    <row r="537" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="537" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M537" s="1" t="s">
         <v>2067</v>
       </c>
@@ -33583,7 +34175,7 @@
         <v>5017</v>
       </c>
     </row>
-    <row r="538" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="538" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M538" s="1" t="s">
         <v>2068</v>
       </c>
@@ -33591,7 +34183,7 @@
         <v>2681</v>
       </c>
     </row>
-    <row r="539" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="539" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M539" s="1" t="s">
         <v>2069</v>
       </c>
@@ -33599,7 +34191,7 @@
         <v>5018</v>
       </c>
     </row>
-    <row r="540" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="540" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M540" s="1" t="s">
         <v>311</v>
       </c>
@@ -33607,7 +34199,7 @@
         <v>5019</v>
       </c>
     </row>
-    <row r="541" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="541" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M541" s="1" t="s">
         <v>2070</v>
       </c>
@@ -33615,7 +34207,7 @@
         <v>5020</v>
       </c>
     </row>
-    <row r="542" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="542" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M542" s="1" t="s">
         <v>2071</v>
       </c>
@@ -33623,7 +34215,7 @@
         <v>5021</v>
       </c>
     </row>
-    <row r="543" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="543" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M543" s="1" t="s">
         <v>2072</v>
       </c>
@@ -33631,7 +34223,7 @@
         <v>5022</v>
       </c>
     </row>
-    <row r="544" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="544" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M544" s="1" t="s">
         <v>2073</v>
       </c>
@@ -33639,7 +34231,7 @@
         <v>5023</v>
       </c>
     </row>
-    <row r="545" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="545" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M545" s="1" t="s">
         <v>2074</v>
       </c>
@@ -33647,7 +34239,7 @@
         <v>5024</v>
       </c>
     </row>
-    <row r="546" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="546" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M546" s="1" t="s">
         <v>2075</v>
       </c>
@@ -33655,7 +34247,7 @@
         <v>5025</v>
       </c>
     </row>
-    <row r="547" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="547" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M547" s="1" t="s">
         <v>2076</v>
       </c>
@@ -33663,7 +34255,7 @@
         <v>5026</v>
       </c>
     </row>
-    <row r="548" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="548" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M548" s="1" t="s">
         <v>2077</v>
       </c>
@@ -33671,7 +34263,7 @@
         <v>5027</v>
       </c>
     </row>
-    <row r="549" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="549" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M549" s="1" t="s">
         <v>2078</v>
       </c>
@@ -33679,7 +34271,7 @@
         <v>5028</v>
       </c>
     </row>
-    <row r="550" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="550" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M550" s="1" t="s">
         <v>2079</v>
       </c>
@@ -33687,7 +34279,7 @@
         <v>4466</v>
       </c>
     </row>
-    <row r="551" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="551" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M551" s="1" t="s">
         <v>2080</v>
       </c>
@@ -33695,7 +34287,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="552" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="552" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M552" s="1" t="s">
         <v>2081</v>
       </c>
@@ -33703,7 +34295,7 @@
         <v>5029</v>
       </c>
     </row>
-    <row r="553" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="553" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M553" s="1" t="s">
         <v>2082</v>
       </c>
@@ -33711,7 +34303,7 @@
         <v>5030</v>
       </c>
     </row>
-    <row r="554" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="554" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M554" s="1" t="s">
         <v>2083</v>
       </c>
@@ -33719,7 +34311,7 @@
         <v>5031</v>
       </c>
     </row>
-    <row r="555" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="555" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M555" s="1" t="s">
         <v>2084</v>
       </c>
@@ -33727,7 +34319,7 @@
         <v>5032</v>
       </c>
     </row>
-    <row r="556" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="556" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M556" s="1" t="s">
         <v>2085</v>
       </c>
@@ -33735,7 +34327,7 @@
         <v>5033</v>
       </c>
     </row>
-    <row r="557" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="557" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M557" s="1" t="s">
         <v>2086</v>
       </c>
@@ -33743,7 +34335,7 @@
         <v>5034</v>
       </c>
     </row>
-    <row r="558" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="558" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M558" s="1" t="s">
         <v>2087</v>
       </c>
@@ -33751,7 +34343,7 @@
         <v>5035</v>
       </c>
     </row>
-    <row r="559" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="559" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M559" s="1" t="s">
         <v>2088</v>
       </c>
@@ -33759,7 +34351,7 @@
         <v>5036</v>
       </c>
     </row>
-    <row r="560" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="560" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M560" s="1" t="s">
         <v>2089</v>
       </c>
@@ -33767,7 +34359,7 @@
         <v>5037</v>
       </c>
     </row>
-    <row r="561" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="561" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M561" s="1" t="s">
         <v>2090</v>
       </c>
@@ -33775,7 +34367,7 @@
         <v>5038</v>
       </c>
     </row>
-    <row r="562" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="562" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M562" s="1" t="s">
         <v>2091</v>
       </c>
@@ -33783,7 +34375,7 @@
         <v>5039</v>
       </c>
     </row>
-    <row r="563" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="563" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M563" s="1" t="s">
         <v>2092</v>
       </c>
@@ -33791,7 +34383,7 @@
         <v>5040</v>
       </c>
     </row>
-    <row r="564" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="564" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M564" s="1" t="s">
         <v>2093</v>
       </c>
@@ -33799,7 +34391,7 @@
         <v>5041</v>
       </c>
     </row>
-    <row r="565" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="565" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M565" s="1" t="s">
         <v>2094</v>
       </c>
@@ -33807,7 +34399,7 @@
         <v>5042</v>
       </c>
     </row>
-    <row r="566" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="566" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M566" s="1" t="s">
         <v>2095</v>
       </c>
@@ -33815,7 +34407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="567" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="567" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M567" s="1" t="s">
         <v>2096</v>
       </c>
@@ -33823,7 +34415,7 @@
         <v>3684</v>
       </c>
     </row>
-    <row r="568" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="568" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M568" s="1" t="s">
         <v>2097</v>
       </c>
@@ -33831,7 +34423,7 @@
         <v>5043</v>
       </c>
     </row>
-    <row r="569" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="569" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M569" s="1" t="s">
         <v>2098</v>
       </c>
@@ -33839,7 +34431,7 @@
         <v>5044</v>
       </c>
     </row>
-    <row r="570" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="570" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M570" s="1" t="s">
         <v>2099</v>
       </c>
@@ -33847,7 +34439,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="571" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="571" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M571" s="1" t="s">
         <v>2100</v>
       </c>
@@ -33855,7 +34447,7 @@
         <v>5045</v>
       </c>
     </row>
-    <row r="572" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="572" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M572" s="1" t="s">
         <v>2101</v>
       </c>
@@ -33863,7 +34455,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="573" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="573" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M573" s="1" t="s">
         <v>2102</v>
       </c>
@@ -33871,7 +34463,7 @@
         <v>3686</v>
       </c>
     </row>
-    <row r="574" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="574" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M574" s="1" t="s">
         <v>2103</v>
       </c>
@@ -33879,7 +34471,7 @@
         <v>5046</v>
       </c>
     </row>
-    <row r="575" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="575" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M575" s="1" t="s">
         <v>2104</v>
       </c>
@@ -33887,7 +34479,7 @@
         <v>5047</v>
       </c>
     </row>
-    <row r="576" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="576" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M576" s="1" t="s">
         <v>2105</v>
       </c>
@@ -33895,7 +34487,7 @@
         <v>5048</v>
       </c>
     </row>
-    <row r="577" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="577" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M577" s="1" t="s">
         <v>2106</v>
       </c>
@@ -33903,7 +34495,7 @@
         <v>5049</v>
       </c>
     </row>
-    <row r="578" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="578" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M578" s="1" t="s">
         <v>2107</v>
       </c>
@@ -33911,7 +34503,7 @@
         <v>5050</v>
       </c>
     </row>
-    <row r="579" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="579" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M579" s="1" t="s">
         <v>2108</v>
       </c>
@@ -33919,7 +34511,7 @@
         <v>5051</v>
       </c>
     </row>
-    <row r="580" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="580" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M580" s="1" t="s">
         <v>2109</v>
       </c>
@@ -33927,7 +34519,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="581" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="581" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M581" s="1" t="s">
         <v>2110</v>
       </c>
@@ -33935,7 +34527,7 @@
         <v>5052</v>
       </c>
     </row>
-    <row r="582" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="582" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M582" s="1" t="s">
         <v>2111</v>
       </c>
@@ -33943,7 +34535,7 @@
         <v>5053</v>
       </c>
     </row>
-    <row r="583" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="583" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M583" s="1" t="s">
         <v>2112</v>
       </c>
@@ -33951,7 +34543,7 @@
         <v>5054</v>
       </c>
     </row>
-    <row r="584" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="584" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M584" s="1" t="s">
         <v>2113</v>
       </c>
@@ -33959,7 +34551,7 @@
         <v>5055</v>
       </c>
     </row>
-    <row r="585" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="585" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M585" s="1" t="s">
         <v>2114</v>
       </c>
@@ -33967,7 +34559,7 @@
         <v>5056</v>
       </c>
     </row>
-    <row r="586" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="586" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M586" s="1" t="s">
         <v>2115</v>
       </c>
@@ -33975,7 +34567,7 @@
         <v>5057</v>
       </c>
     </row>
-    <row r="587" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="587" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M587" s="1" t="s">
         <v>2116</v>
       </c>
@@ -33983,7 +34575,7 @@
         <v>5058</v>
       </c>
     </row>
-    <row r="588" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="588" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M588" s="1" t="s">
         <v>2117</v>
       </c>
@@ -33991,7 +34583,7 @@
         <v>5059</v>
       </c>
     </row>
-    <row r="589" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="589" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M589" s="1" t="s">
         <v>2118</v>
       </c>
@@ -33999,7 +34591,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="590" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="590" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M590" s="1" t="s">
         <v>2119</v>
       </c>
@@ -34007,7 +34599,7 @@
         <v>5061</v>
       </c>
     </row>
-    <row r="591" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="591" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M591" s="1" t="s">
         <v>2120</v>
       </c>
@@ -34015,7 +34607,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="592" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="592" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M592" s="1" t="s">
         <v>2121</v>
       </c>
@@ -34023,7 +34615,7 @@
         <v>5062</v>
       </c>
     </row>
-    <row r="593" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="593" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M593" s="1" t="s">
         <v>2122</v>
       </c>
@@ -34031,7 +34623,7 @@
         <v>5063</v>
       </c>
     </row>
-    <row r="594" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="594" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M594" s="1" t="s">
         <v>2123</v>
       </c>
@@ -34039,7 +34631,7 @@
         <v>5064</v>
       </c>
     </row>
-    <row r="595" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="595" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M595" s="1" t="s">
         <v>2124</v>
       </c>
@@ -34047,7 +34639,7 @@
         <v>5065</v>
       </c>
     </row>
-    <row r="596" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="596" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M596" s="1" t="s">
         <v>2125</v>
       </c>
@@ -34055,7 +34647,7 @@
         <v>5066</v>
       </c>
     </row>
-    <row r="597" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="597" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M597" s="1" t="s">
         <v>2126</v>
       </c>
@@ -34063,7 +34655,7 @@
         <v>5067</v>
       </c>
     </row>
-    <row r="598" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="598" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M598" s="1" t="s">
         <v>2127</v>
       </c>
@@ -34071,7 +34663,7 @@
         <v>5068</v>
       </c>
     </row>
-    <row r="599" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="599" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M599" s="1" t="s">
         <v>2128</v>
       </c>
@@ -34079,7 +34671,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="600" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="600" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M600" s="1" t="s">
         <v>2129</v>
       </c>
@@ -34087,7 +34679,7 @@
         <v>5069</v>
       </c>
     </row>
-    <row r="601" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="601" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M601" s="1" t="s">
         <v>2130</v>
       </c>
@@ -34095,7 +34687,7 @@
         <v>5070</v>
       </c>
     </row>
-    <row r="602" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="602" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M602" s="1" t="s">
         <v>2131</v>
       </c>
@@ -34103,7 +34695,7 @@
         <v>5071</v>
       </c>
     </row>
-    <row r="603" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="603" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M603" s="1" t="s">
         <v>2132</v>
       </c>
@@ -34111,7 +34703,7 @@
         <v>5072</v>
       </c>
     </row>
-    <row r="604" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="604" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M604" s="1" t="s">
         <v>2133</v>
       </c>
@@ -34119,7 +34711,7 @@
         <v>5073</v>
       </c>
     </row>
-    <row r="605" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="605" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M605" s="1" t="s">
         <v>2134</v>
       </c>
@@ -34127,7 +34719,7 @@
         <v>5074</v>
       </c>
     </row>
-    <row r="606" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="606" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M606" s="1" t="s">
         <v>2135</v>
       </c>
@@ -34135,7 +34727,7 @@
         <v>5075</v>
       </c>
     </row>
-    <row r="607" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="607" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M607" s="1" t="s">
         <v>2136</v>
       </c>
@@ -34143,7 +34735,7 @@
         <v>5076</v>
       </c>
     </row>
-    <row r="608" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="608" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M608" s="1" t="s">
         <v>2137</v>
       </c>
@@ -34151,7 +34743,7 @@
         <v>5077</v>
       </c>
     </row>
-    <row r="609" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="609" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M609" s="1" t="s">
         <v>2138</v>
       </c>
@@ -34159,7 +34751,7 @@
         <v>5078</v>
       </c>
     </row>
-    <row r="610" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="610" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M610" s="1" t="s">
         <v>2139</v>
       </c>
@@ -34167,7 +34759,7 @@
         <v>5079</v>
       </c>
     </row>
-    <row r="611" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="611" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M611" s="1" t="s">
         <v>2140</v>
       </c>
@@ -34175,7 +34767,7 @@
         <v>3245</v>
       </c>
     </row>
-    <row r="612" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="612" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M612" s="1" t="s">
         <v>2141</v>
       </c>
@@ -34183,7 +34775,7 @@
         <v>5080</v>
       </c>
     </row>
-    <row r="613" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="613" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M613" s="1" t="s">
         <v>2142</v>
       </c>
@@ -34191,7 +34783,7 @@
         <v>5081</v>
       </c>
     </row>
-    <row r="614" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="614" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M614" s="1" t="s">
         <v>2143</v>
       </c>
@@ -34199,7 +34791,7 @@
         <v>5082</v>
       </c>
     </row>
-    <row r="615" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="615" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M615" s="1" t="s">
         <v>2144</v>
       </c>
@@ -34207,7 +34799,7 @@
         <v>5083</v>
       </c>
     </row>
-    <row r="616" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="616" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M616" s="1" t="s">
         <v>2145</v>
       </c>
@@ -34215,7 +34807,7 @@
         <v>5084</v>
       </c>
     </row>
-    <row r="617" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="617" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M617" s="1" t="s">
         <v>2146</v>
       </c>
@@ -34223,7 +34815,7 @@
         <v>5085</v>
       </c>
     </row>
-    <row r="618" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="618" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M618" s="1" t="s">
         <v>2147</v>
       </c>
@@ -34231,7 +34823,7 @@
         <v>5086</v>
       </c>
     </row>
-    <row r="619" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="619" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M619" s="1" t="s">
         <v>2148</v>
       </c>
@@ -34239,7 +34831,7 @@
         <v>5087</v>
       </c>
     </row>
-    <row r="620" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="620" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M620" s="1" t="s">
         <v>2149</v>
       </c>
@@ -34247,7 +34839,7 @@
         <v>5088</v>
       </c>
     </row>
-    <row r="621" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="621" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M621" s="1" t="s">
         <v>2150</v>
       </c>
@@ -34255,7 +34847,7 @@
         <v>5089</v>
       </c>
     </row>
-    <row r="622" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="622" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M622" s="1" t="s">
         <v>2151</v>
       </c>
@@ -34263,7 +34855,7 @@
         <v>5090</v>
       </c>
     </row>
-    <row r="623" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="623" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M623" s="1" t="s">
         <v>2152</v>
       </c>
@@ -34271,7 +34863,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="624" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="624" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M624" s="1" t="s">
         <v>1399</v>
       </c>
@@ -34279,7 +34871,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="625" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="625" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M625" s="1" t="s">
         <v>2153</v>
       </c>
@@ -34287,7 +34879,7 @@
         <v>5092</v>
       </c>
     </row>
-    <row r="626" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="626" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M626" s="1" t="s">
         <v>2154</v>
       </c>
@@ -34295,7 +34887,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="627" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="627" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M627" s="1" t="s">
         <v>2155</v>
       </c>
@@ -34303,7 +34895,7 @@
         <v>5094</v>
       </c>
     </row>
-    <row r="628" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="628" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M628" s="1" t="s">
         <v>2156</v>
       </c>
@@ -34311,7 +34903,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="629" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="629" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M629" s="1" t="s">
         <v>2157</v>
       </c>
@@ -34319,7 +34911,7 @@
         <v>5096</v>
       </c>
     </row>
-    <row r="630" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="630" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M630" s="1" t="s">
         <v>2158</v>
       </c>
@@ -34327,7 +34919,7 @@
         <v>5097</v>
       </c>
     </row>
-    <row r="631" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="631" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M631" s="1" t="s">
         <v>2159</v>
       </c>
@@ -34335,7 +34927,7 @@
         <v>5098</v>
       </c>
     </row>
-    <row r="632" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="632" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M632" s="1" t="s">
         <v>2160</v>
       </c>
@@ -34343,7 +34935,7 @@
         <v>5099</v>
       </c>
     </row>
-    <row r="633" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="633" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M633" s="1" t="s">
         <v>2161</v>
       </c>
@@ -34351,7 +34943,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="634" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="634" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M634" s="1" t="s">
         <v>2162</v>
       </c>
@@ -34359,7 +34951,7 @@
         <v>5101</v>
       </c>
     </row>
-    <row r="635" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="635" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M635" s="1" t="s">
         <v>2163</v>
       </c>
@@ -34367,7 +34959,7 @@
         <v>5102</v>
       </c>
     </row>
-    <row r="636" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="636" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M636" s="1" t="s">
         <v>2164</v>
       </c>
@@ -34375,7 +34967,7 @@
         <v>4506</v>
       </c>
     </row>
-    <row r="637" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="637" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M637" s="1" t="s">
         <v>2165</v>
       </c>
@@ -34383,7 +34975,7 @@
         <v>5103</v>
       </c>
     </row>
-    <row r="638" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="638" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M638" s="1" t="s">
         <v>2166</v>
       </c>
@@ -34391,7 +34983,7 @@
         <v>5104</v>
       </c>
     </row>
-    <row r="639" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="639" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M639" s="1" t="s">
         <v>2167</v>
       </c>
@@ -34399,7 +34991,7 @@
         <v>5105</v>
       </c>
     </row>
-    <row r="640" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="640" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M640" s="1" t="s">
         <v>2168</v>
       </c>
@@ -34407,7 +34999,7 @@
         <v>3709</v>
       </c>
     </row>
-    <row r="641" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="641" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M641" s="1" t="s">
         <v>2169</v>
       </c>
@@ -34415,7 +35007,7 @@
         <v>5106</v>
       </c>
     </row>
-    <row r="642" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="642" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M642" s="1" t="s">
         <v>2170</v>
       </c>
@@ -34423,7 +35015,7 @@
         <v>5107</v>
       </c>
     </row>
-    <row r="643" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="643" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M643" s="1" t="s">
         <v>2171</v>
       </c>
@@ -34431,7 +35023,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="644" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="644" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M644" s="1" t="s">
         <v>2172</v>
       </c>
@@ -34439,7 +35031,7 @@
         <v>5109</v>
       </c>
     </row>
-    <row r="645" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="645" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M645" s="1" t="s">
         <v>2173</v>
       </c>
@@ -34447,7 +35039,7 @@
         <v>5110</v>
       </c>
     </row>
-    <row r="646" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="646" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M646" s="1" t="s">
         <v>2174</v>
       </c>
@@ -34455,7 +35047,7 @@
         <v>5111</v>
       </c>
     </row>
-    <row r="647" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="647" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M647" s="1" t="s">
         <v>2175</v>
       </c>
@@ -34463,1042 +35055,1042 @@
         <v>5112</v>
       </c>
     </row>
-    <row r="648" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="648" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M648" s="1" t="s">
         <v>2176</v>
       </c>
     </row>
-    <row r="649" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="649" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M649" s="1" t="s">
         <v>2177</v>
       </c>
     </row>
-    <row r="650" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="650" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M650" s="1" t="s">
         <v>2178</v>
       </c>
     </row>
-    <row r="651" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="651" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M651" s="1" t="s">
         <v>2179</v>
       </c>
     </row>
-    <row r="652" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="652" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M652" s="1" t="s">
         <v>2180</v>
       </c>
     </row>
-    <row r="653" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="653" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M653" s="1" t="s">
         <v>2181</v>
       </c>
     </row>
-    <row r="654" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="654" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M654" s="1" t="s">
         <v>2182</v>
       </c>
     </row>
-    <row r="655" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="655" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M655" s="1" t="s">
         <v>2183</v>
       </c>
     </row>
-    <row r="656" spans="13:25" x14ac:dyDescent="0.25">
+    <row r="656" spans="13:25" x14ac:dyDescent="0.35">
       <c r="M656" s="1" t="s">
         <v>2184</v>
       </c>
     </row>
-    <row r="657" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="657" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M657" s="1" t="s">
         <v>2185</v>
       </c>
     </row>
-    <row r="658" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="658" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M658" s="1" t="s">
         <v>2186</v>
       </c>
     </row>
-    <row r="659" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="659" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M659" s="1" t="s">
         <v>2187</v>
       </c>
     </row>
-    <row r="660" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="660" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M660" s="1" t="s">
         <v>2188</v>
       </c>
     </row>
-    <row r="661" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="661" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M661" s="1" t="s">
         <v>2189</v>
       </c>
     </row>
-    <row r="662" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="662" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M662" s="1" t="s">
         <v>2190</v>
       </c>
     </row>
-    <row r="663" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="663" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M663" s="1" t="s">
         <v>2191</v>
       </c>
     </row>
-    <row r="664" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="664" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M664" s="1" t="s">
         <v>2192</v>
       </c>
     </row>
-    <row r="665" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="665" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M665" s="1" t="s">
         <v>2193</v>
       </c>
     </row>
-    <row r="666" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="666" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M666" s="1" t="s">
         <v>2194</v>
       </c>
     </row>
-    <row r="667" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="667" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M667" s="1" t="s">
         <v>2195</v>
       </c>
     </row>
-    <row r="668" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="668" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M668" s="1" t="s">
         <v>2196</v>
       </c>
     </row>
-    <row r="669" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="669" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M669" s="1" t="s">
         <v>2197</v>
       </c>
     </row>
-    <row r="670" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="670" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M670" s="1" t="s">
         <v>2198</v>
       </c>
     </row>
-    <row r="671" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="671" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M671" s="1" t="s">
         <v>2199</v>
       </c>
     </row>
-    <row r="672" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="672" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M672" s="1" t="s">
         <v>2200</v>
       </c>
     </row>
-    <row r="673" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="673" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M673" s="1" t="s">
         <v>2201</v>
       </c>
     </row>
-    <row r="674" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="674" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M674" s="1" t="s">
         <v>2202</v>
       </c>
     </row>
-    <row r="675" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="675" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M675" s="1" t="s">
         <v>2203</v>
       </c>
     </row>
-    <row r="676" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="676" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M676" s="1" t="s">
         <v>2204</v>
       </c>
     </row>
-    <row r="677" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="677" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M677" s="1" t="s">
         <v>1412</v>
       </c>
     </row>
-    <row r="678" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="678" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M678" s="1" t="s">
         <v>2205</v>
       </c>
     </row>
-    <row r="679" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="679" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M679" s="1" t="s">
         <v>2206</v>
       </c>
     </row>
-    <row r="680" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="680" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M680" s="1" t="s">
         <v>2207</v>
       </c>
     </row>
-    <row r="681" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="681" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M681" s="1" t="s">
         <v>2208</v>
       </c>
     </row>
-    <row r="682" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="682" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M682" s="1" t="s">
         <v>2209</v>
       </c>
     </row>
-    <row r="683" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="683" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M683" s="1" t="s">
         <v>2210</v>
       </c>
     </row>
-    <row r="684" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="684" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M684" s="1" t="s">
         <v>2211</v>
       </c>
     </row>
-    <row r="685" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="685" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M685" s="1" t="s">
         <v>2212</v>
       </c>
     </row>
-    <row r="686" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="686" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M686" s="1" t="s">
         <v>2213</v>
       </c>
     </row>
-    <row r="687" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="687" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M687" s="1" t="s">
         <v>2214</v>
       </c>
     </row>
-    <row r="688" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="688" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M688" s="1" t="s">
         <v>2215</v>
       </c>
     </row>
-    <row r="689" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="689" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M689" s="1" t="s">
         <v>2216</v>
       </c>
     </row>
-    <row r="690" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="690" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M690" s="1" t="s">
         <v>2217</v>
       </c>
     </row>
-    <row r="691" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="691" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M691" s="1" t="s">
         <v>2218</v>
       </c>
     </row>
-    <row r="692" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="692" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M692" s="1" t="s">
         <v>2219</v>
       </c>
     </row>
-    <row r="693" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="693" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M693" s="1" t="s">
         <v>2220</v>
       </c>
     </row>
-    <row r="694" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="694" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M694" s="1" t="s">
         <v>2221</v>
       </c>
     </row>
-    <row r="695" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="695" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M695" s="1" t="s">
         <v>2222</v>
       </c>
     </row>
-    <row r="696" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="696" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M696" s="1" t="s">
         <v>2223</v>
       </c>
     </row>
-    <row r="697" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="697" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M697" s="1" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="698" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="698" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M698" s="1" t="s">
         <v>2225</v>
       </c>
     </row>
-    <row r="699" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="699" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M699" s="1" t="s">
         <v>2226</v>
       </c>
     </row>
-    <row r="700" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="700" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M700" s="1" t="s">
         <v>2227</v>
       </c>
     </row>
-    <row r="701" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="701" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M701" s="1" t="s">
         <v>2228</v>
       </c>
     </row>
-    <row r="702" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="702" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M702" s="1" t="s">
         <v>2229</v>
       </c>
     </row>
-    <row r="703" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="703" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M703" s="1" t="s">
         <v>2230</v>
       </c>
     </row>
-    <row r="704" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="704" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M704" s="1" t="s">
         <v>2231</v>
       </c>
     </row>
-    <row r="705" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="705" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M705" s="1" t="s">
         <v>2232</v>
       </c>
     </row>
-    <row r="706" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="706" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M706" s="1" t="s">
         <v>2233</v>
       </c>
     </row>
-    <row r="707" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="707" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M707" s="1" t="s">
         <v>2234</v>
       </c>
     </row>
-    <row r="708" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="708" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M708" s="1" t="s">
         <v>2235</v>
       </c>
     </row>
-    <row r="709" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="709" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M709" s="1" t="s">
         <v>2236</v>
       </c>
     </row>
-    <row r="710" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="710" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M710" s="1" t="s">
         <v>2237</v>
       </c>
     </row>
-    <row r="711" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="711" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M711" s="1" t="s">
         <v>2238</v>
       </c>
     </row>
-    <row r="712" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="712" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M712" s="1" t="s">
         <v>2239</v>
       </c>
     </row>
-    <row r="713" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="713" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M713" s="1" t="s">
         <v>2240</v>
       </c>
     </row>
-    <row r="714" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="714" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M714" s="1" t="s">
         <v>2241</v>
       </c>
     </row>
-    <row r="715" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="715" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M715" s="1" t="s">
         <v>2242</v>
       </c>
     </row>
-    <row r="716" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="716" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M716" s="1" t="s">
         <v>2243</v>
       </c>
     </row>
-    <row r="717" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="717" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M717" s="1" t="s">
         <v>2244</v>
       </c>
     </row>
-    <row r="718" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="718" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M718" s="1" t="s">
         <v>2245</v>
       </c>
     </row>
-    <row r="719" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="719" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M719" s="1" t="s">
         <v>2246</v>
       </c>
     </row>
-    <row r="720" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="720" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M720" s="1" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="721" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="721" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M721" s="1" t="s">
         <v>2248</v>
       </c>
     </row>
-    <row r="722" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="722" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M722" s="1" t="s">
         <v>2249</v>
       </c>
     </row>
-    <row r="723" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="723" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M723" s="1" t="s">
         <v>2250</v>
       </c>
     </row>
-    <row r="724" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="724" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M724" s="1" t="s">
         <v>2251</v>
       </c>
     </row>
-    <row r="725" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="725" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M725" s="1" t="s">
         <v>2252</v>
       </c>
     </row>
-    <row r="726" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="726" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M726" s="1" t="s">
         <v>2253</v>
       </c>
     </row>
-    <row r="727" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="727" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M727" s="1" t="s">
         <v>2254</v>
       </c>
     </row>
-    <row r="728" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="728" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M728" s="1" t="s">
         <v>2255</v>
       </c>
     </row>
-    <row r="729" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="729" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M729" s="1" t="s">
         <v>2256</v>
       </c>
     </row>
-    <row r="730" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="730" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M730" s="1" t="s">
         <v>2257</v>
       </c>
     </row>
-    <row r="731" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="731" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M731" s="1" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="732" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="732" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M732" s="1" t="s">
         <v>2259</v>
       </c>
     </row>
-    <row r="733" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="733" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M733" s="1" t="s">
         <v>2260</v>
       </c>
     </row>
-    <row r="734" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="734" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M734" s="1" t="s">
         <v>2261</v>
       </c>
     </row>
-    <row r="735" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="735" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M735" s="1" t="s">
         <v>2262</v>
       </c>
     </row>
-    <row r="736" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="736" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M736" s="1" t="s">
         <v>2263</v>
       </c>
     </row>
-    <row r="737" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="737" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M737" s="1" t="s">
         <v>2264</v>
       </c>
     </row>
-    <row r="738" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="738" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M738" s="1" t="s">
         <v>1429</v>
       </c>
     </row>
-    <row r="739" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="739" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M739" s="1" t="s">
         <v>2265</v>
       </c>
     </row>
-    <row r="740" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="740" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M740" s="1" t="s">
         <v>2266</v>
       </c>
     </row>
-    <row r="741" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="741" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M741" s="1" t="s">
         <v>2267</v>
       </c>
     </row>
-    <row r="742" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="742" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M742" s="1" t="s">
         <v>2268</v>
       </c>
     </row>
-    <row r="743" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="743" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M743" s="1" t="s">
         <v>2269</v>
       </c>
     </row>
-    <row r="744" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="744" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M744" s="1" t="s">
         <v>2270</v>
       </c>
     </row>
-    <row r="745" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="745" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M745" s="1" t="s">
         <v>2271</v>
       </c>
     </row>
-    <row r="746" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="746" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M746" s="1" t="s">
         <v>2272</v>
       </c>
     </row>
-    <row r="747" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="747" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M747" s="1" t="s">
         <v>2273</v>
       </c>
     </row>
-    <row r="748" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="748" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M748" s="1" t="s">
         <v>2274</v>
       </c>
     </row>
-    <row r="749" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="749" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M749" s="1" t="s">
         <v>2275</v>
       </c>
     </row>
-    <row r="750" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="750" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M750" s="1" t="s">
         <v>2276</v>
       </c>
     </row>
-    <row r="751" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="751" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M751" s="1" t="s">
         <v>2277</v>
       </c>
     </row>
-    <row r="752" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="752" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M752" s="1" t="s">
         <v>2278</v>
       </c>
     </row>
-    <row r="753" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="753" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M753" s="1" t="s">
         <v>2279</v>
       </c>
     </row>
-    <row r="754" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="754" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M754" s="1" t="s">
         <v>2280</v>
       </c>
     </row>
-    <row r="755" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="755" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M755" s="1" t="s">
         <v>2281</v>
       </c>
     </row>
-    <row r="756" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="756" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M756" s="1" t="s">
         <v>2282</v>
       </c>
     </row>
-    <row r="757" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="757" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M757" s="1" t="s">
         <v>2283</v>
       </c>
     </row>
-    <row r="758" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="758" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M758" s="1" t="s">
         <v>2284</v>
       </c>
     </row>
-    <row r="759" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="759" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M759" s="1" t="s">
         <v>2285</v>
       </c>
     </row>
-    <row r="760" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="760" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M760" s="1" t="s">
         <v>2286</v>
       </c>
     </row>
-    <row r="761" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="761" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M761" s="1" t="s">
         <v>2287</v>
       </c>
     </row>
-    <row r="762" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="762" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M762" s="1" t="s">
         <v>2288</v>
       </c>
     </row>
-    <row r="763" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="763" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M763" s="1" t="s">
         <v>2289</v>
       </c>
     </row>
-    <row r="764" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="764" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M764" s="1" t="s">
         <v>2290</v>
       </c>
     </row>
-    <row r="765" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="765" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M765" s="1" t="s">
         <v>2291</v>
       </c>
     </row>
-    <row r="766" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="766" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M766" s="1" t="s">
         <v>2292</v>
       </c>
     </row>
-    <row r="767" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="767" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M767" s="1" t="s">
         <v>2293</v>
       </c>
     </row>
-    <row r="768" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="768" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M768" s="1" t="s">
         <v>2294</v>
       </c>
     </row>
-    <row r="769" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="769" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M769" s="1" t="s">
         <v>2295</v>
       </c>
     </row>
-    <row r="770" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="770" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M770" s="1" t="s">
         <v>2296</v>
       </c>
     </row>
-    <row r="771" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="771" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M771" s="1" t="s">
         <v>2297</v>
       </c>
     </row>
-    <row r="772" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="772" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M772" s="1" t="s">
         <v>2298</v>
       </c>
     </row>
-    <row r="773" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="773" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M773" s="1" t="s">
         <v>2299</v>
       </c>
     </row>
-    <row r="774" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="774" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M774" s="1" t="s">
         <v>2300</v>
       </c>
     </row>
-    <row r="775" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="775" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M775" s="1" t="s">
         <v>2301</v>
       </c>
     </row>
-    <row r="776" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="776" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M776" s="1" t="s">
         <v>2302</v>
       </c>
     </row>
-    <row r="777" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="777" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M777" s="1" t="s">
         <v>2303</v>
       </c>
     </row>
-    <row r="778" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="778" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M778" s="1" t="s">
         <v>2304</v>
       </c>
     </row>
-    <row r="779" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="779" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M779" s="1" t="s">
         <v>2305</v>
       </c>
     </row>
-    <row r="780" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="780" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M780" s="1" t="s">
         <v>2306</v>
       </c>
     </row>
-    <row r="781" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="781" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M781" s="1" t="s">
         <v>2307</v>
       </c>
     </row>
-    <row r="782" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="782" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M782" s="1" t="s">
         <v>2308</v>
       </c>
     </row>
-    <row r="783" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="783" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M783" s="1" t="s">
         <v>2309</v>
       </c>
     </row>
-    <row r="784" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="784" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M784" s="1" t="s">
         <v>2310</v>
       </c>
     </row>
-    <row r="785" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="785" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M785" s="1" t="s">
         <v>2311</v>
       </c>
     </row>
-    <row r="786" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="786" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M786" s="1" t="s">
         <v>2312</v>
       </c>
     </row>
-    <row r="787" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="787" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M787" s="1" t="s">
         <v>2313</v>
       </c>
     </row>
-    <row r="788" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="788" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M788" s="1" t="s">
         <v>2314</v>
       </c>
     </row>
-    <row r="789" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="789" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M789" s="1" t="s">
         <v>2315</v>
       </c>
     </row>
-    <row r="790" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="790" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M790" s="1" t="s">
         <v>2316</v>
       </c>
     </row>
-    <row r="791" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="791" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M791" s="1" t="s">
         <v>2317</v>
       </c>
     </row>
-    <row r="792" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="792" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M792" s="1" t="s">
         <v>2318</v>
       </c>
     </row>
-    <row r="793" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="793" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M793" s="1" t="s">
         <v>2319</v>
       </c>
     </row>
-    <row r="794" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="794" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M794" s="1" t="s">
         <v>2320</v>
       </c>
     </row>
-    <row r="795" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="795" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M795" s="1" t="s">
         <v>2321</v>
       </c>
     </row>
-    <row r="796" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="796" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M796" s="1" t="s">
         <v>2322</v>
       </c>
     </row>
-    <row r="797" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="797" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M797" s="1" t="s">
         <v>2323</v>
       </c>
     </row>
-    <row r="798" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="798" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M798" s="1" t="s">
         <v>2324</v>
       </c>
     </row>
-    <row r="799" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="799" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M799" s="1" t="s">
         <v>2325</v>
       </c>
     </row>
-    <row r="800" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="800" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M800" s="1" t="s">
         <v>2326</v>
       </c>
     </row>
-    <row r="801" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="801" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M801" s="1" t="s">
         <v>2327</v>
       </c>
     </row>
-    <row r="802" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="802" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M802" s="1" t="s">
         <v>2328</v>
       </c>
     </row>
-    <row r="803" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="803" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M803" s="1" t="s">
         <v>2329</v>
       </c>
     </row>
-    <row r="804" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="804" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M804" s="1" t="s">
         <v>2330</v>
       </c>
     </row>
-    <row r="805" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="805" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M805" s="1" t="s">
         <v>2331</v>
       </c>
     </row>
-    <row r="806" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="806" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M806" s="1" t="s">
         <v>2332</v>
       </c>
     </row>
-    <row r="807" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="807" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M807" s="1" t="s">
         <v>2333</v>
       </c>
     </row>
-    <row r="808" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="808" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M808" s="1" t="s">
         <v>2334</v>
       </c>
     </row>
-    <row r="809" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="809" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M809" s="1" t="s">
         <v>2335</v>
       </c>
     </row>
-    <row r="810" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="810" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M810" s="1" t="s">
         <v>2336</v>
       </c>
     </row>
-    <row r="811" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="811" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M811" s="1" t="s">
         <v>2337</v>
       </c>
     </row>
-    <row r="812" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="812" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M812" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="813" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="813" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M813" s="1" t="s">
         <v>2338</v>
       </c>
     </row>
-    <row r="814" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="814" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M814" s="1" t="s">
         <v>2339</v>
       </c>
     </row>
-    <row r="815" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="815" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M815" s="1" t="s">
         <v>2340</v>
       </c>
     </row>
-    <row r="816" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="816" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M816" s="1" t="s">
         <v>2341</v>
       </c>
     </row>
-    <row r="817" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="817" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M817" s="1" t="s">
         <v>2342</v>
       </c>
     </row>
-    <row r="818" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="818" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M818" s="1" t="s">
         <v>2343</v>
       </c>
     </row>
-    <row r="819" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="819" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M819" s="1" t="s">
         <v>2344</v>
       </c>
     </row>
-    <row r="820" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="820" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M820" s="1" t="s">
         <v>2345</v>
       </c>
     </row>
-    <row r="821" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="821" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M821" s="1" t="s">
         <v>2346</v>
       </c>
     </row>
-    <row r="822" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="822" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M822" s="1" t="s">
         <v>2347</v>
       </c>
     </row>
-    <row r="823" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="823" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M823" s="1" t="s">
         <v>2348</v>
       </c>
     </row>
-    <row r="824" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="824" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M824" s="1" t="s">
         <v>2349</v>
       </c>
     </row>
-    <row r="825" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="825" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M825" s="1" t="s">
         <v>2350</v>
       </c>
     </row>
-    <row r="826" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="826" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M826" s="1" t="s">
         <v>2351</v>
       </c>
     </row>
-    <row r="827" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="827" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M827" s="1" t="s">
         <v>2352</v>
       </c>
     </row>
-    <row r="828" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="828" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M828" s="1" t="s">
         <v>2353</v>
       </c>
     </row>
-    <row r="829" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="829" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M829" s="1" t="s">
         <v>2354</v>
       </c>
     </row>
-    <row r="830" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="830" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M830" s="1" t="s">
         <v>2355</v>
       </c>
     </row>
-    <row r="831" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="831" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M831" s="1" t="s">
         <v>2356</v>
       </c>
     </row>
-    <row r="832" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="832" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M832" s="1" t="s">
         <v>2357</v>
       </c>
     </row>
-    <row r="833" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="833" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M833" s="1" t="s">
         <v>2358</v>
       </c>
     </row>
-    <row r="834" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="834" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M834" s="1" t="s">
         <v>2359</v>
       </c>
     </row>
-    <row r="835" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="835" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M835" s="1" t="s">
         <v>2360</v>
       </c>
     </row>
-    <row r="836" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="836" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M836" s="1" t="s">
         <v>2361</v>
       </c>
     </row>
-    <row r="837" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="837" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M837" s="1" t="s">
         <v>2362</v>
       </c>
     </row>
-    <row r="838" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="838" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M838" s="1" t="s">
         <v>2363</v>
       </c>
     </row>
-    <row r="839" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="839" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M839" s="1" t="s">
         <v>2364</v>
       </c>
     </row>
-    <row r="840" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="840" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M840" s="1" t="s">
         <v>2365</v>
       </c>
     </row>
-    <row r="841" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="841" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M841" s="1" t="s">
         <v>2366</v>
       </c>
     </row>
-    <row r="842" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="842" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M842" s="1" t="s">
         <v>2367</v>
       </c>
     </row>
-    <row r="843" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="843" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M843" s="1" t="s">
         <v>2368</v>
       </c>
     </row>
-    <row r="844" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="844" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M844" s="1" t="s">
         <v>2369</v>
       </c>
     </row>
-    <row r="845" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="845" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M845" s="1" t="s">
         <v>2370</v>
       </c>
     </row>
-    <row r="846" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="846" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M846" s="1" t="s">
         <v>2371</v>
       </c>
     </row>
-    <row r="847" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="847" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M847" s="1" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="848" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="848" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M848" s="1" t="s">
         <v>2372</v>
       </c>
     </row>
-    <row r="849" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="849" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M849" s="1" t="s">
         <v>2373</v>
       </c>
     </row>
-    <row r="850" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="850" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M850" s="1" t="s">
         <v>2374</v>
       </c>
     </row>
-    <row r="851" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="851" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M851" s="1" t="s">
         <v>2375</v>
       </c>
     </row>
-    <row r="852" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="852" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M852" s="1" t="s">
         <v>2376</v>
       </c>
     </row>
-    <row r="853" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="853" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M853" s="1" t="s">
         <v>2377</v>
       </c>
     </row>
-    <row r="854" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="854" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M854" s="1" t="s">
         <v>2378</v>
       </c>
     </row>
-    <row r="855" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="855" spans="13:13" x14ac:dyDescent="0.35">
       <c r="M855" s="1" t="s">
         <v>2379</v>
       </c>
